--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Valencia Basket.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2168.76</v>
+        <v>2490.48</v>
       </c>
       <c r="C2" t="n">
-        <v>2171.06</v>
+        <v>2492.22</v>
       </c>
       <c r="D2" t="n">
-        <v>121.4614059491677</v>
+        <v>120.8159793276677</v>
       </c>
       <c r="E2" t="n">
-        <v>106.3996388860741</v>
+        <v>107.1735240067089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5581632653061225</v>
+        <v>0.5605790645879732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1309368394877533</v>
+        <v>0.1335608058508469</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3763940520446097</v>
+        <v>0.372937293729373</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2290816326530612</v>
+        <v>0.2200445434298441</v>
       </c>
       <c r="J2" t="n">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="L2" t="n">
-        <v>236</v>
+        <v>279</v>
       </c>
       <c r="M2" t="n">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="N2" t="n">
-        <v>855</v>
+        <v>974</v>
       </c>
       <c r="O2" t="n">
-        <v>1181</v>
+        <v>1335</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6025510204081632</v>
+        <v>0.5946547884187082</v>
       </c>
       <c r="Q2" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="R2" t="n">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1673469387755102</v>
+        <v>0.1652561247216036</v>
       </c>
       <c r="T2" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="U2" t="n">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08367346938775511</v>
+        <v>0.08374164810690424</v>
       </c>
       <c r="W2" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="X2" t="n">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1127551020408163</v>
+        <v>0.110022271714922</v>
       </c>
       <c r="Z2" t="n">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="AA2" t="n">
-        <v>695</v>
+        <v>796</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3545918367346939</v>
+        <v>0.3545657015590201</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7239627434377646</v>
+        <v>0.7295880149812735</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4024390243902439</v>
+        <v>0.398921832884097</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3353658536585366</v>
+        <v>0.3617021276595745</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3967611336032389</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3496402877697842</v>
+        <v>0.3479899497487437</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.447925486875529</v>
+        <v>1.459176029962547</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6707317073170732</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.093886462882096</v>
+        <v>1.078619367209971</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.010471204188482</v>
+        <v>1.006864988558352</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9061728395061729</v>
+        <v>0.8938053097345132</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.858267716535433</v>
+        <v>1.87248322147651</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.724035608308605</v>
+        <v>1.689567430025445</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.816023738872404</v>
+        <v>5.712468193384224</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.540059347181009</v>
+        <v>7.402035623409669</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.45571428571428</v>
+        <v>77.82749999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>77.53785714285716</v>
+        <v>77.88187500000001</v>
       </c>
       <c r="D3" t="n">
-        <v>121.4614059491677</v>
+        <v>120.8159793276677</v>
       </c>
       <c r="E3" t="n">
-        <v>106.3996388860741</v>
+        <v>107.1735240067089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5581632653061224</v>
+        <v>0.5605790645879732</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1309368394877533</v>
+        <v>0.1335608058508469</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3763940520446096</v>
+        <v>0.372937293729373</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2290816326530612</v>
+        <v>0.2200445434298441</v>
       </c>
       <c r="J3" t="n">
-        <v>13.78571428571429</v>
+        <v>13.75</v>
       </c>
       <c r="K3" t="n">
-        <v>13.10714285714286</v>
+        <v>12.625</v>
       </c>
       <c r="L3" t="n">
-        <v>8.428571428571429</v>
+        <v>8.71875</v>
       </c>
       <c r="M3" t="n">
-        <v>11.57142857142857</v>
+        <v>11.8125</v>
       </c>
       <c r="N3" t="n">
-        <v>30.53571428571428</v>
+        <v>30.4375</v>
       </c>
       <c r="O3" t="n">
-        <v>42.17857142857143</v>
+        <v>41.71875</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6025510204081633</v>
+        <v>0.5946547884187082</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.714285714285714</v>
+        <v>4.625</v>
       </c>
       <c r="R3" t="n">
-        <v>11.71428571428571</v>
+        <v>11.59375</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1673469387755102</v>
+        <v>0.1652561247216036</v>
       </c>
       <c r="T3" t="n">
-        <v>1.964285714285714</v>
+        <v>2.125</v>
       </c>
       <c r="U3" t="n">
-        <v>5.857142857142857</v>
+        <v>5.875</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08367346938775509</v>
+        <v>0.08374164810690424</v>
       </c>
       <c r="W3" t="n">
-        <v>3.25</v>
+        <v>3.0625</v>
       </c>
       <c r="X3" t="n">
-        <v>7.892857142857143</v>
+        <v>7.71875</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1127551020408163</v>
+        <v>0.110022271714922</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.678571428571429</v>
+        <v>8.65625</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.82142857142857</v>
+        <v>24.875</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3545918367346939</v>
+        <v>0.3545657015590201</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7239627434377646</v>
+        <v>0.7295880149812735</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4024390243902439</v>
+        <v>0.398921832884097</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3353658536585366</v>
+        <v>0.3617021276595745</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3967611336032389</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3496402877697842</v>
+        <v>0.3479899497487437</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.447925486875529</v>
+        <v>1.459176029962547</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6707317073170732</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.093886462882096</v>
+        <v>1.078619367209971</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.010471204188482</v>
+        <v>1.006864988558352</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9061728395061729</v>
+        <v>0.8938053097345132</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.858267716535433</v>
+        <v>1.87248322147651</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.724035608308605</v>
+        <v>1.689567430025445</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.816023738872403</v>
+        <v>5.712468193384224</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.540059347181009</v>
+        <v>7.402035623409669</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2173.36</v>
+        <v>2493.96</v>
       </c>
       <c r="C4" t="n">
-        <v>2171.06</v>
+        <v>2492.22</v>
       </c>
       <c r="D4" t="n">
-        <v>106.3996388860741</v>
+        <v>107.1735240067089</v>
       </c>
       <c r="E4" t="n">
-        <v>121.4614059491677</v>
+        <v>120.8159793276677</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5119110640550556</v>
+        <v>0.5155236329935126</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1535147647446511</v>
+        <v>0.1532279555112975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2994296577946768</v>
+        <v>0.2990810359231412</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1990471148755956</v>
+        <v>0.2066728452270621</v>
       </c>
       <c r="J4" t="n">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="K4" t="n">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="L4" t="n">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="M4" t="n">
-        <v>357</v>
+        <v>407</v>
       </c>
       <c r="N4" t="n">
-        <v>726</v>
+        <v>857</v>
       </c>
       <c r="O4" t="n">
-        <v>995</v>
+        <v>1177</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5267337215457915</v>
+        <v>0.5454124189063948</v>
       </c>
       <c r="Q4" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="R4" t="n">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1821069348861832</v>
+        <v>0.1797961075069509</v>
       </c>
       <c r="T4" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="U4" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1011116993118052</v>
+        <v>0.09870250231696015</v>
       </c>
       <c r="W4" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="X4" t="n">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.119640021175225</v>
+        <v>0.1227988878591288</v>
       </c>
       <c r="Z4" t="n">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="AA4" t="n">
-        <v>627</v>
+        <v>699</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3319216516675489</v>
+        <v>0.3239110287303059</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7296482412060301</v>
+        <v>0.7281223449447749</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4127906976744186</v>
+        <v>0.4149484536082474</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3193717277486911</v>
+        <v>0.3192488262910798</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3849557522123894</v>
+        <v>0.369811320754717</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3014354066985646</v>
+        <v>0.3104434907010014</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.45929648241206</v>
+        <v>1.45624468988955</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6387434554973822</v>
+        <v>0.6384976525821596</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9706916764361079</v>
+        <v>0.9802904564315352</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7655786350148368</v>
+        <v>0.7837150127226463</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.873015873015873</v>
+        <v>0.8547486033519553</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.827956989247312</v>
+        <v>1.842592592592593</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.227748691099476</v>
+        <v>1.226544622425629</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.945026178010472</v>
+        <v>4.938215102974828</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.172774869109948</v>
+        <v>6.164759725400458</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.61999999999999</v>
+        <v>77.93624999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>77.53785714285716</v>
+        <v>77.88187500000001</v>
       </c>
       <c r="D5" t="n">
-        <v>106.3996388860741</v>
+        <v>107.1735240067089</v>
       </c>
       <c r="E5" t="n">
-        <v>121.4614059491677</v>
+        <v>120.8159793276677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5119110640550555</v>
+        <v>0.5155236329935126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1535147647446511</v>
+        <v>0.1532279555112975</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2994296577946768</v>
+        <v>0.2990810359231412</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1990471148755955</v>
+        <v>0.2066728452270621</v>
       </c>
       <c r="J5" t="n">
-        <v>9.214285714285714</v>
+        <v>9.625</v>
       </c>
       <c r="K5" t="n">
-        <v>9.821428571428571</v>
+        <v>9.5625</v>
       </c>
       <c r="L5" t="n">
-        <v>6.071428571428571</v>
+        <v>6.21875</v>
       </c>
       <c r="M5" t="n">
-        <v>12.75</v>
+        <v>12.71875</v>
       </c>
       <c r="N5" t="n">
-        <v>25.92857142857143</v>
+        <v>26.78125</v>
       </c>
       <c r="O5" t="n">
-        <v>35.53571428571428</v>
+        <v>36.78125</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5267337215457913</v>
+        <v>0.5454124189063948</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.071428571428571</v>
+        <v>5.03125</v>
       </c>
       <c r="R5" t="n">
-        <v>12.28571428571429</v>
+        <v>12.125</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1821069348861832</v>
+        <v>0.1797961075069509</v>
       </c>
       <c r="T5" t="n">
-        <v>2.178571428571428</v>
+        <v>2.125</v>
       </c>
       <c r="U5" t="n">
-        <v>6.821428571428571</v>
+        <v>6.65625</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1011116993118052</v>
+        <v>0.09870250231696015</v>
       </c>
       <c r="W5" t="n">
-        <v>3.107142857142857</v>
+        <v>3.0625</v>
       </c>
       <c r="X5" t="n">
-        <v>8.071428571428571</v>
+        <v>8.28125</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.119640021175225</v>
+        <v>0.1227988878591288</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.75</v>
+        <v>6.78125</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.39285714285714</v>
+        <v>21.84375</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3319216516675489</v>
+        <v>0.3239110287303059</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7296482412060301</v>
+        <v>0.7281223449447749</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4127906976744186</v>
+        <v>0.4149484536082474</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3193717277486911</v>
+        <v>0.3192488262910798</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3849557522123894</v>
+        <v>0.369811320754717</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3014354066985646</v>
+        <v>0.3104434907010014</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45929648241206</v>
+        <v>1.45624468988955</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6387434554973822</v>
+        <v>0.6384976525821596</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9706916764361079</v>
+        <v>0.9802904564315352</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7655786350148367</v>
+        <v>0.7837150127226463</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.873015873015873</v>
+        <v>0.8547486033519553</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.827956989247312</v>
+        <v>1.842592592592593</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.227748691099476</v>
+        <v>1.226544622425629</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.945026178010472</v>
+        <v>4.938215102974828</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.172774869109949</v>
+        <v>6.164759725400458</v>
       </c>
     </row>
     <row r="7">
@@ -1419,147 +1419,147 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="H8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I8" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J8" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N8" t="n">
         <v>14</v>
       </c>
-      <c r="M8" t="n">
-        <v>20</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>38</v>
+      </c>
+      <c r="R8" t="n">
+        <v>55</v>
+      </c>
+      <c r="S8" t="n">
+        <v>58</v>
+      </c>
+      <c r="T8" t="n">
+        <v>253</v>
+      </c>
+      <c r="U8" t="n">
+        <v>51</v>
+      </c>
+      <c r="V8" t="n">
+        <v>35</v>
+      </c>
+      <c r="W8" t="n">
+        <v>41</v>
+      </c>
+      <c r="X8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>93</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AH8" t="n">
         <v>12</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="AI8" t="n">
         <v>35</v>
       </c>
-      <c r="Q8" t="n">
-        <v>35</v>
-      </c>
-      <c r="R8" t="n">
-        <v>46</v>
-      </c>
-      <c r="S8" t="n">
-        <v>51</v>
-      </c>
-      <c r="T8" t="n">
-        <v>219</v>
-      </c>
-      <c r="U8" t="n">
-        <v>46</v>
-      </c>
-      <c r="V8" t="n">
-        <v>32</v>
-      </c>
-      <c r="W8" t="n">
-        <v>31</v>
-      </c>
-      <c r="X8" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>30</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>0.367</v>
+        <v>0.343</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>486:47</t>
+          <t>555:10</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>267.56</v>
+        <v>303.32</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.491</v>
+        <v>0.504</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.535</v>
+        <v>0.541</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.931</v>
+        <v>0.946</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.131</v>
+        <v>0.125</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.199</v>
+        <v>0.178</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.239</v>
+        <v>0.238</v>
       </c>
       <c r="AW8" t="n">
         <v>0.03</v>
@@ -1568,7 +1568,7 @@
         <v>0.092</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="9">
@@ -1578,156 +1578,156 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" t="n">
+        <v>259</v>
+      </c>
+      <c r="D9" t="n">
+        <v>75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>127</v>
+      </c>
+      <c r="F9" t="n">
+        <v>29</v>
+      </c>
+      <c r="G9" t="n">
+        <v>72</v>
+      </c>
+      <c r="H9" t="n">
+        <v>22</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>76</v>
+      </c>
+      <c r="L9" t="n">
         <v>19</v>
       </c>
-      <c r="C9" t="n">
-        <v>208</v>
-      </c>
-      <c r="D9" t="n">
-        <v>57</v>
-      </c>
-      <c r="E9" t="n">
-        <v>97</v>
-      </c>
-      <c r="F9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G9" t="n">
-        <v>58</v>
-      </c>
-      <c r="H9" t="n">
-        <v>19</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="M9" t="n">
         <v>26</v>
       </c>
-      <c r="J9" t="n">
-        <v>45</v>
-      </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" t="n">
-        <v>21</v>
-      </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S9" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T9" t="n">
-        <v>251</v>
+        <v>314</v>
       </c>
       <c r="U9" t="n">
+        <v>48</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>31</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>83</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC9" t="n">
         <v>44</v>
       </c>
-      <c r="V9" t="n">
-        <v>7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>23</v>
-      </c>
-      <c r="X9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>49</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>35</v>
-      </c>
       <c r="AD9" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="AH9" t="n">
         <v>9</v>
       </c>
       <c r="AI9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.6</v>
+        <v>0.429</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.372</v>
+        <v>0.392</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>402:57</t>
+          <t>489:40</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>192.44</v>
+        <v>247.2</v>
       </c>
       <c r="AP9" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>0.61</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>0.625</v>
-      </c>
       <c r="AR9" t="n">
-        <v>1.081</v>
+        <v>1.048</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.135</v>
+        <v>0.142</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.123</v>
+        <v>0.111</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.731</v>
+        <v>1.571</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.208</v>
+        <v>0.22</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.028</v>
+        <v>0.041</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.156</v>
+        <v>0.166</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.053</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="10">
@@ -1737,37 +1737,37 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>25</v>
+      </c>
+      <c r="C10" t="n">
+        <v>164</v>
+      </c>
+      <c r="D10" t="n">
         <v>24</v>
       </c>
-      <c r="C10" t="n">
-        <v>154</v>
-      </c>
-      <c r="D10" t="n">
-        <v>21</v>
-      </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" t="n">
         <v>16</v>
-      </c>
-      <c r="I10" t="n">
-        <v>22</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
       </c>
       <c r="K10" t="n">
         <v>47</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M10" t="n">
         <v>8</v>
@@ -1785,34 +1785,34 @@
         <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T10" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="U10" t="n">
         <v>21</v>
       </c>
       <c r="V10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="W10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.725</v>
+        <v>0.733</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
@@ -1842,51 +1842,51 @@
         <v>0.333</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.321</v>
+        <v>0.328</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>421:18</t>
+          <t>437:45</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>163.68</v>
+        <v>169.56</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.493</v>
+        <v>0.507</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.514</v>
+        <v>0.527</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.967</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.114</v>
+        <v>0.117</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.071</v>
+        <v>1.143</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.119</v>
+        <v>0.115</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="11">
@@ -1896,100 +1896,100 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="H11" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I11" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L11" t="n">
         <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="S11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T11" t="n">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="U11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="V11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="Z11" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.73</v>
+        <v>0.745</v>
       </c>
       <c r="AB11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.406</v>
+        <v>0.441</v>
       </c>
       <c r="AE11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="AH11" t="n">
         <v>2</v>
@@ -2001,51 +2001,51 @@
         <v>0.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.343</v>
+        <v>0.357</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>466:49</t>
+          <t>535:38</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>217.24</v>
+        <v>249.44</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.587</v>
+        <v>0.603</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.613</v>
+        <v>0.628</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.146</v>
+        <v>1.171</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.273</v>
+        <v>0.261</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.143</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
         <v>0.203</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="12">
@@ -2055,40 +2055,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="D12" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E12" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="J12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
         <v>13</v>
@@ -2097,49 +2097,49 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R12" t="n">
+        <v>36</v>
+      </c>
+      <c r="S12" t="n">
+        <v>89</v>
+      </c>
+      <c r="T12" t="n">
+        <v>483</v>
+      </c>
+      <c r="U12" t="n">
         <v>31</v>
       </c>
-      <c r="S12" t="n">
-        <v>74</v>
-      </c>
-      <c r="T12" t="n">
-        <v>440</v>
-      </c>
-      <c r="U12" t="n">
-        <v>22</v>
-      </c>
       <c r="V12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="W12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="Z12" t="n">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.753</v>
+        <v>0.763</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.52</v>
+        <v>0.483</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2154,57 +2154,57 @@
         <v>10</v>
       </c>
       <c r="AI12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="AK12" t="n">
         <v>12</v>
       </c>
       <c r="AL12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.364</v>
+        <v>0.324</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>547:14</t>
+          <t>614:35</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>243.28</v>
+        <v>274.12</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.67</v>
+        <v>0.652</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.143</v>
+        <v>1.127</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.164</v>
+        <v>0.161</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.239</v>
+        <v>0.258</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.525</v>
+        <v>1.5</v>
       </c>
       <c r="AV12" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AX12" t="n">
         <v>0.193</v>
       </c>
-      <c r="AW12" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.198</v>
-      </c>
       <c r="AY12" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2214,156 +2214,156 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
+        <v>84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>64</v>
+      </c>
+      <c r="I13" t="n">
+        <v>78</v>
+      </c>
+      <c r="J13" t="n">
+        <v>98</v>
+      </c>
+      <c r="K13" t="n">
+        <v>42</v>
+      </c>
+      <c r="L13" t="n">
+        <v>35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>13</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>46</v>
+      </c>
+      <c r="R13" t="n">
+        <v>41</v>
+      </c>
+      <c r="S13" t="n">
+        <v>87</v>
+      </c>
+      <c r="T13" t="n">
+        <v>348</v>
+      </c>
+      <c r="U13" t="n">
+        <v>32</v>
+      </c>
+      <c r="V13" t="n">
+        <v>35</v>
+      </c>
+      <c r="W13" t="n">
+        <v>15</v>
+      </c>
+      <c r="X13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>115</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL13" t="n">
         <v>67</v>
       </c>
-      <c r="H13" t="n">
-        <v>52</v>
-      </c>
-      <c r="I13" t="n">
-        <v>64</v>
-      </c>
-      <c r="J13" t="n">
-        <v>76</v>
-      </c>
-      <c r="K13" t="n">
-        <v>34</v>
-      </c>
-      <c r="L13" t="n">
-        <v>31</v>
-      </c>
-      <c r="M13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N13" t="n">
-        <v>12</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>40</v>
-      </c>
-      <c r="R13" t="n">
-        <v>34</v>
-      </c>
-      <c r="S13" t="n">
-        <v>75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>283</v>
-      </c>
-      <c r="U13" t="n">
-        <v>24</v>
-      </c>
-      <c r="V13" t="n">
-        <v>33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>11</v>
-      </c>
-      <c r="X13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>93</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.796</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
       <c r="AM13" t="n">
-        <v>0.418</v>
+        <v>0.373</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>383:41</t>
+          <t>475:38</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>204.16</v>
+        <v>250.32</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.624</v>
+        <v>0.619</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.004</v>
+        <v>1.011</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.196</v>
+        <v>0.184</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.382</v>
+        <v>0.376</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.232</v>
+        <v>0.229</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="AX13" t="n">
         <v>0.094</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="14">
@@ -2516,13 +2516,13 @@
         <v>0.199</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="15">
@@ -2532,156 +2532,156 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
       </c>
       <c r="I15" t="n">
+        <v>34</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22</v>
+      </c>
+      <c r="K15" t="n">
+        <v>49</v>
+      </c>
+      <c r="L15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M15" t="n">
+        <v>19</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+      <c r="R15" t="n">
         <v>32</v>
       </c>
-      <c r="J15" t="n">
-        <v>20</v>
-      </c>
-      <c r="K15" t="n">
-        <v>39</v>
-      </c>
-      <c r="L15" t="n">
-        <v>12</v>
-      </c>
-      <c r="M15" t="n">
-        <v>18</v>
-      </c>
-      <c r="N15" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>13</v>
-      </c>
-      <c r="R15" t="n">
-        <v>29</v>
-      </c>
       <c r="S15" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="T15" t="n">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="U15" t="n">
         <v>18</v>
       </c>
       <c r="V15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Z15" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.597</v>
+        <v>0.614</v>
       </c>
       <c r="AB15" t="n">
         <v>10</v>
       </c>
       <c r="AC15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.4</v>
+        <v>0.357</v>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.091</v>
+        <v>0.154</v>
       </c>
       <c r="AK15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.636</v>
+        <v>0.571</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>279:28</t>
+          <t>339:51</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>109.08</v>
+        <v>132.96</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.549</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.546</v>
+        <v>0.553</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.963</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.119</v>
+        <v>0.15</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.183</v>
+        <v>0.153</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.538</v>
+        <v>1.1</v>
       </c>
       <c r="AV15" t="n">
         <v>0.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.045</v>
+        <v>0.053</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.149</v>
+        <v>0.154</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="16">
@@ -2691,22 +2691,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H16" t="n">
         <v>62</v>
@@ -2715,43 +2715,43 @@
         <v>71</v>
       </c>
       <c r="J16" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K16" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S16" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T16" t="n">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="V16" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W16" t="n">
         <v>20</v>
@@ -2760,31 +2760,31 @@
         <v>12</v>
       </c>
       <c r="Y16" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Z16" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.797</v>
+        <v>0.803</v>
       </c>
       <c r="AB16" t="n">
         <v>10</v>
       </c>
       <c r="AC16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.286</v>
+        <v>0.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
@@ -2796,51 +2796,51 @@
         <v>0.579</v>
       </c>
       <c r="AK16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AL16" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.384</v>
+        <v>0.368</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>460:06</t>
+          <t>497:16</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>298.24</v>
+        <v>315.24</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.61</v>
+        <v>0.602</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.096</v>
+        <v>1.079</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.262</v>
+        <v>0.247</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.833</v>
+        <v>2.788</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.282</v>
+        <v>0.276</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.102</v>
+        <v>0.105</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.104</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="17">
@@ -2850,91 +2850,91 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C17" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G17" t="n">
+        <v>70</v>
+      </c>
+      <c r="H17" t="n">
+        <v>39</v>
+      </c>
+      <c r="I17" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" t="n">
+        <v>79</v>
+      </c>
+      <c r="K17" t="n">
+        <v>50</v>
+      </c>
+      <c r="L17" t="n">
+        <v>23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>17</v>
+      </c>
+      <c r="N17" t="n">
         <v>22</v>
       </c>
-      <c r="G17" t="n">
-        <v>58</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>37</v>
       </c>
-      <c r="I17" t="n">
-        <v>47</v>
-      </c>
-      <c r="J17" t="n">
-        <v>67</v>
-      </c>
-      <c r="K17" t="n">
-        <v>43</v>
-      </c>
-      <c r="L17" t="n">
-        <v>20</v>
-      </c>
-      <c r="M17" t="n">
-        <v>13</v>
-      </c>
-      <c r="N17" t="n">
-        <v>18</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>30</v>
-      </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="R17" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S17" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="T17" t="n">
-        <v>256</v>
+        <v>311</v>
       </c>
       <c r="U17" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="V17" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="W17" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="Z17" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.71</v>
+        <v>0.722</v>
       </c>
       <c r="AB17" t="n">
         <v>19</v>
       </c>
       <c r="AC17" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.442</v>
+        <v>0.404</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -2949,57 +2949,57 @@
         <v>5</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.333</v>
+        <v>0.263</v>
       </c>
       <c r="AK17" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.395</v>
+        <v>0.451</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>475:54</t>
+          <t>559:30</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>211.68</v>
+        <v>248</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.547</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.586</v>
+        <v>0.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.006</v>
+        <v>1.02</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.142</v>
+        <v>0.149</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.23</v>
+        <v>0.206</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.233</v>
+        <v>2.135</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="AX17" t="n">
         <v>0.096</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="18">
@@ -3009,16 +3009,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -3027,49 +3027,49 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" t="n">
+        <v>46</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" t="n">
         <v>44</v>
       </c>
-      <c r="J18" t="n">
-        <v>19</v>
-      </c>
-      <c r="K18" t="n">
-        <v>44</v>
-      </c>
-      <c r="L18" t="n">
-        <v>41</v>
-      </c>
       <c r="M18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R18" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S18" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="T18" t="n">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="U18" t="n">
         <v>14</v>
       </c>
       <c r="V18" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -3078,22 +3078,22 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="Z18" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.578</v>
+        <v>0.606</v>
       </c>
       <c r="AB18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.429</v>
+        <v>0.44</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3124,41 +3124,41 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>344:52</t>
+          <t>372:28</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>106.36</v>
+        <v>119.24</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.625</v>
+        <v>0.639</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.586</v>
+        <v>0.605</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.006</v>
+        <v>1.048</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.141</v>
+        <v>0.134</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.236</v>
+        <v>0.229</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.267</v>
+        <v>1.25</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.134</v>
+        <v>0.139</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19">
@@ -3168,40 +3168,40 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>28</v>
+      </c>
+      <c r="C19" t="n">
+        <v>206</v>
+      </c>
+      <c r="D19" t="n">
+        <v>39</v>
+      </c>
+      <c r="E19" t="n">
+        <v>69</v>
+      </c>
+      <c r="F19" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" t="n">
+        <v>92</v>
+      </c>
+      <c r="H19" t="n">
+        <v>38</v>
+      </c>
+      <c r="I19" t="n">
+        <v>46</v>
+      </c>
+      <c r="J19" t="n">
+        <v>80</v>
+      </c>
+      <c r="K19" t="n">
+        <v>27</v>
+      </c>
+      <c r="L19" t="n">
         <v>24</v>
       </c>
-      <c r="C19" t="n">
-        <v>187</v>
-      </c>
-      <c r="D19" t="n">
-        <v>37</v>
-      </c>
-      <c r="E19" t="n">
-        <v>64</v>
-      </c>
-      <c r="F19" t="n">
-        <v>26</v>
-      </c>
-      <c r="G19" t="n">
-        <v>77</v>
-      </c>
-      <c r="H19" t="n">
-        <v>35</v>
-      </c>
-      <c r="I19" t="n">
-        <v>43</v>
-      </c>
-      <c r="J19" t="n">
-        <v>74</v>
-      </c>
-      <c r="K19" t="n">
-        <v>25</v>
-      </c>
-      <c r="L19" t="n">
-        <v>22</v>
-      </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N19" t="n">
         <v>9</v>
@@ -3210,22 +3210,22 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="S19" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="T19" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="U19" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="V19" t="n">
         <v>23</v>
@@ -3237,22 +3237,22 @@
         <v>14</v>
       </c>
       <c r="Y19" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Z19" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.831</v>
+        <v>0.829</v>
       </c>
       <c r="AB19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.318</v>
+        <v>0.32</v>
       </c>
       <c r="AE19" t="n">
         <v>6</v>
@@ -3264,60 +3264,60 @@
         <v>0.429</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.319</v>
+        <v>0.301</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>435:35</t>
+          <t>490:34</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>183.92</v>
+        <v>206.24</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.539</v>
+        <v>0.522</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.585</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.017</v>
+        <v>0.999</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.13</v>
+        <v>0.121</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.248</v>
+        <v>0.236</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.083</v>
+        <v>3.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">
@@ -3467,7 +3467,7 @@
         <v>2</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.663</v>
+        <v>0.662</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -3482,578 +3482,578 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>#24 M. COSTELLO</t>
+          <t>#23 A. CÁRDENAS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>241</v>
+        <v>-7</v>
       </c>
       <c r="U21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.634</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AO21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>1</v>
       </c>
-      <c r="AF21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>64</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>427:23</t>
-        </is>
-      </c>
-      <c r="AO21" t="n">
-        <v>174.4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.101</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0.075</v>
-      </c>
       <c r="AT21" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.769</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.178</v>
+        <v>0.196</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>#32 I. NOGUÉS</t>
+          <t>#24 M. COSTELLO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>220</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="F22" t="n">
+        <v>40</v>
+      </c>
+      <c r="G22" t="n">
+        <v>105</v>
+      </c>
+      <c r="H22" t="n">
+        <v>18</v>
+      </c>
+      <c r="I22" t="n">
+        <v>38</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29</v>
+      </c>
+      <c r="K22" t="n">
+        <v>76</v>
+      </c>
+      <c r="L22" t="n">
+        <v>43</v>
+      </c>
+      <c r="M22" t="n">
+        <v>24</v>
+      </c>
+      <c r="N22" t="n">
+        <v>26</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" t="n">
+        <v>51</v>
+      </c>
+      <c r="S22" t="n">
+        <v>39</v>
+      </c>
+      <c r="T22" t="n">
+        <v>285</v>
+      </c>
+      <c r="U22" t="n">
+        <v>25</v>
+      </c>
+      <c r="V22" t="n">
+        <v>22</v>
+      </c>
+      <c r="W22" t="n">
+        <v>24</v>
+      </c>
+      <c r="X22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>77</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>12</v>
-      </c>
-      <c r="K22" t="n">
-        <v>17</v>
-      </c>
-      <c r="L22" t="n">
-        <v>9</v>
-      </c>
-      <c r="M22" t="n">
-        <v>9</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>30</v>
-      </c>
-      <c r="S22" t="n">
-        <v>7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>18</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AF22" t="n">
         <v>5</v>
       </c>
-      <c r="Z22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1</v>
-      </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.333</v>
+        <v>0.52</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.338</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>111:21</t>
+          <t>494:46</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>21.76</v>
+        <v>198.72</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.219</v>
+        <v>0.605</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.282</v>
+        <v>0.599</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.46</v>
+        <v>1.107</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.184</v>
+        <v>0.075</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.188</v>
+        <v>0.108</v>
       </c>
       <c r="AU22" t="n">
-        <v>3</v>
+        <v>1.933</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.175</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.092</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.013</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>#77 Y. SIMA</t>
+          <t>#32 I. NOGUÉS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>12</v>
+      </c>
+      <c r="N23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="n">
-        <v>10</v>
-      </c>
-      <c r="H23" t="n">
-        <v>10</v>
-      </c>
-      <c r="I23" t="n">
-        <v>18</v>
-      </c>
-      <c r="J23" t="n">
-        <v>5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>15</v>
-      </c>
-      <c r="L23" t="n">
-        <v>14</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>7</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T23" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="U23" t="n">
         <v>6</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1</v>
       </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AI23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
         <v>3</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>10</v>
-      </c>
       <c r="AM23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>137:23</t>
+          <t>143:01</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>51.92</v>
+        <v>26.76</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.528</v>
+        <v>0.237</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.546</v>
+        <v>0.289</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.924</v>
+        <v>0.448</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.154</v>
+        <v>0.224</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.278</v>
+        <v>0.158</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.625</v>
+        <v>2.333</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.164</v>
+        <v>0.081</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.106</v>
+        <v>0.066</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.116</v>
+        <v>0.15</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#77 Y. SIMA</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="n">
+        <v>61</v>
+      </c>
+      <c r="D24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" t="n">
+        <v>34</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" t="n">
         <v>28</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
+        <v>19</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>11</v>
+      </c>
+      <c r="R24" t="n">
+        <v>27</v>
+      </c>
+      <c r="S24" t="n">
+        <v>21</v>
+      </c>
+      <c r="T24" t="n">
+        <v>63</v>
+      </c>
+      <c r="U24" t="n">
+        <v>8</v>
+      </c>
+      <c r="V24" t="n">
+        <v>17</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z24" t="n">
         <v>56</v>
       </c>
-      <c r="L24" t="n">
-        <v>48</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="AA24" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -4068,51 +4068,51 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>173:38</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>0.893</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="25">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4149,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4164,19 +4164,19 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
         <v>0</v>
@@ -4281,144 +4281,144 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>2637</v>
+        <v>3011</v>
       </c>
       <c r="D26" t="n">
-        <v>593</v>
+        <v>696</v>
       </c>
       <c r="E26" t="n">
-        <v>1044</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="G26" t="n">
-        <v>916</v>
+        <v>1043</v>
       </c>
       <c r="H26" t="n">
-        <v>449</v>
+        <v>494</v>
       </c>
       <c r="I26" t="n">
-        <v>629</v>
+        <v>692</v>
       </c>
       <c r="J26" t="n">
-        <v>581</v>
+        <v>664</v>
       </c>
       <c r="K26" t="n">
-        <v>737</v>
+        <v>839</v>
       </c>
       <c r="L26" t="n">
-        <v>405</v>
+        <v>452</v>
       </c>
       <c r="M26" t="n">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="N26" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="Q26" t="n">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="R26" t="n">
-        <v>541</v>
+        <v>620</v>
       </c>
       <c r="S26" t="n">
-        <v>626</v>
+        <v>707</v>
       </c>
       <c r="T26" t="n">
-        <v>3295</v>
+        <v>3747</v>
       </c>
       <c r="U26" t="n">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="V26" t="n">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="W26" t="n">
-        <v>236</v>
+        <v>279</v>
       </c>
       <c r="X26" t="n">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="Y26" t="n">
-        <v>855</v>
+        <v>974</v>
       </c>
       <c r="Z26" t="n">
-        <v>1181</v>
+        <v>1335</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.724</v>
+        <v>0.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="AC26" t="n">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.402</v>
+        <v>0.399</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="AF26" t="n">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.335</v>
+        <v>0.362</v>
       </c>
       <c r="AH26" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AI26" t="n">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.412</v>
+        <v>0.397</v>
       </c>
       <c r="AK26" t="n">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="AL26" t="n">
-        <v>695</v>
+        <v>796</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2573.76</v>
+        <v>2942.48</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.589</v>
+        <v>0.591</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.025</v>
+        <v>1.023</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.131</v>
+        <v>0.134</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.229</v>
+        <v>0.22</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.724</v>
+        <v>1.69</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2</v>
@@ -4440,144 +4440,144 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>2310</v>
+        <v>2671</v>
       </c>
       <c r="D27" t="n">
-        <v>553</v>
+        <v>640</v>
       </c>
       <c r="E27" t="n">
-        <v>1036</v>
+        <v>1194</v>
       </c>
       <c r="F27" t="n">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="G27" t="n">
-        <v>853</v>
+        <v>964</v>
       </c>
       <c r="H27" t="n">
-        <v>376</v>
+        <v>446</v>
       </c>
       <c r="I27" t="n">
-        <v>494</v>
+        <v>584</v>
       </c>
       <c r="J27" t="n">
-        <v>469</v>
+        <v>536</v>
       </c>
       <c r="K27" t="n">
-        <v>671</v>
+        <v>760</v>
       </c>
       <c r="L27" t="n">
-        <v>315</v>
+        <v>358</v>
       </c>
       <c r="M27" t="n">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="N27" t="n">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>382</v>
+        <v>437</v>
       </c>
       <c r="Q27" t="n">
-        <v>357</v>
+        <v>407</v>
       </c>
       <c r="R27" t="n">
-        <v>627</v>
+        <v>707</v>
       </c>
       <c r="S27" t="n">
-        <v>537</v>
+        <v>617</v>
       </c>
       <c r="T27" t="n">
-        <v>2471</v>
+        <v>2870</v>
       </c>
       <c r="U27" t="n">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="V27" t="n">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="W27" t="n">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="X27" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="Y27" t="n">
-        <v>726</v>
+        <v>857</v>
       </c>
       <c r="Z27" t="n">
-        <v>995</v>
+        <v>1177</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="AB27" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="AC27" t="n">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.413</v>
+        <v>0.415</v>
       </c>
       <c r="AE27" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AF27" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="AG27" t="n">
         <v>0.319</v>
       </c>
       <c r="AH27" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AI27" t="n">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.385</v>
+        <v>0.37</v>
       </c>
       <c r="AK27" t="n">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="AL27" t="n">
-        <v>627</v>
+        <v>699</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.301</v>
+        <v>0.31</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2488.36</v>
+        <v>2851.96</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.512</v>
+        <v>0.516</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.548</v>
+        <v>0.553</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.928</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.199</v>
+        <v>0.207</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.228</v>
+        <v>1.227</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
@@ -4656,147 +4656,147 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C29" t="n">
-        <v>9.222</v>
+        <v>9.567</v>
       </c>
       <c r="D29" t="n">
-        <v>1.333</v>
+        <v>1.567</v>
       </c>
       <c r="E29" t="n">
-        <v>2.741</v>
+        <v>2.933</v>
       </c>
       <c r="F29" t="n">
         <v>1.667</v>
       </c>
       <c r="G29" t="n">
-        <v>5.074</v>
+        <v>5.133</v>
       </c>
       <c r="H29" t="n">
-        <v>1.556</v>
+        <v>1.433</v>
       </c>
       <c r="I29" t="n">
-        <v>1.815</v>
+        <v>1.767</v>
       </c>
       <c r="J29" t="n">
-        <v>1.815</v>
+        <v>1.9</v>
       </c>
       <c r="K29" t="n">
-        <v>1.556</v>
+        <v>1.6</v>
       </c>
       <c r="L29" t="n">
-        <v>0.519</v>
+        <v>0.533</v>
       </c>
       <c r="M29" t="n">
-        <v>0.741</v>
+        <v>0.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.444</v>
+        <v>0.467</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.296</v>
+        <v>1.267</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.296</v>
+        <v>1.267</v>
       </c>
       <c r="R29" t="n">
-        <v>1.704</v>
+        <v>1.833</v>
       </c>
       <c r="S29" t="n">
-        <v>1.889</v>
+        <v>1.933</v>
       </c>
       <c r="T29" t="n">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="U29" t="n">
-        <v>1.704</v>
+        <v>1.7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.185</v>
+        <v>1.167</v>
       </c>
       <c r="W29" t="n">
-        <v>1.148</v>
+        <v>1.367</v>
       </c>
       <c r="X29" t="n">
-        <v>0.63</v>
+        <v>0.733</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.222</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.963</v>
+        <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.75</v>
+        <v>0.742</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.333</v>
+        <v>0.367</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.593</v>
+        <v>0.633</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.579</v>
       </c>
       <c r="AE29" t="n">
         <v>0.333</v>
       </c>
       <c r="AF29" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.333</v>
+        <v>0.345</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.407</v>
+        <v>0.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.111</v>
+        <v>1.167</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.367</v>
+        <v>0.343</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.259</v>
+        <v>1.267</v>
       </c>
       <c r="AL29" t="n">
-        <v>3.963</v>
+        <v>3.967</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>9.91</v>
+        <v>10.111</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.491</v>
+        <v>0.504</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.535</v>
+        <v>0.541</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.931</v>
+        <v>0.946</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.131</v>
+        <v>0.125</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.199</v>
+        <v>0.178</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.239</v>
+        <v>0.238</v>
       </c>
       <c r="AW29" t="n">
         <v>0.03</v>
@@ -4805,7 +4805,7 @@
         <v>0.092</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.06</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="30">
@@ -4815,156 +4815,156 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C30" t="n">
-        <v>10.947</v>
+        <v>11.261</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>3.261</v>
       </c>
       <c r="E30" t="n">
-        <v>5.105</v>
+        <v>5.522</v>
       </c>
       <c r="F30" t="n">
-        <v>1.316</v>
+        <v>1.261</v>
       </c>
       <c r="G30" t="n">
-        <v>3.053</v>
+        <v>3.13</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
       <c r="I30" t="n">
-        <v>1.368</v>
+        <v>1.304</v>
       </c>
       <c r="J30" t="n">
-        <v>2.368</v>
+        <v>2.391</v>
       </c>
       <c r="K30" t="n">
-        <v>3.105</v>
+        <v>3.304</v>
       </c>
       <c r="L30" t="n">
-        <v>0.579</v>
+        <v>0.826</v>
       </c>
       <c r="M30" t="n">
-        <v>1.105</v>
+        <v>1.13</v>
       </c>
       <c r="N30" t="n">
-        <v>0.737</v>
+        <v>0.739</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.368</v>
+        <v>1.522</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.368</v>
+        <v>1.522</v>
       </c>
       <c r="R30" t="n">
-        <v>1.895</v>
+        <v>1.826</v>
       </c>
       <c r="S30" t="n">
-        <v>1.842</v>
+        <v>1.826</v>
       </c>
       <c r="T30" t="n">
-        <v>251</v>
+        <v>314</v>
       </c>
       <c r="U30" t="n">
-        <v>2.316</v>
+        <v>2.087</v>
       </c>
       <c r="V30" t="n">
-        <v>0.368</v>
+        <v>0.522</v>
       </c>
       <c r="W30" t="n">
-        <v>1.211</v>
+        <v>1.348</v>
       </c>
       <c r="X30" t="n">
-        <v>0.474</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.579</v>
+        <v>2.609</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.526</v>
+        <v>3.609</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.731</v>
+        <v>0.723</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.895</v>
+        <v>0.957</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.842</v>
+        <v>1.913</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.526</v>
+        <v>0.652</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.105</v>
+        <v>1.304</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.474</v>
+        <v>0.391</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.789</v>
+        <v>0.913</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.6</v>
+        <v>0.429</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.842</v>
+        <v>0.87</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.263</v>
+        <v>2.217</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.372</v>
+        <v>0.392</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>10.128</v>
+        <v>10.748</v>
       </c>
       <c r="AP30" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>0.61</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>0.625</v>
-      </c>
       <c r="AR30" t="n">
-        <v>1.081</v>
+        <v>1.048</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.135</v>
+        <v>0.142</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.123</v>
+        <v>0.111</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.731</v>
+        <v>1.571</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.208</v>
+        <v>0.22</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.028</v>
+        <v>0.041</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.156</v>
+        <v>0.166</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="31">
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31" t="n">
-        <v>6.417</v>
+        <v>6.56</v>
       </c>
       <c r="D31" t="n">
-        <v>0.875</v>
+        <v>0.96</v>
       </c>
       <c r="E31" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="F31" t="n">
-        <v>1.333</v>
+        <v>1.32</v>
       </c>
       <c r="G31" t="n">
-        <v>4.083</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>0.667</v>
+        <v>0.68</v>
       </c>
       <c r="I31" t="n">
-        <v>0.917</v>
+        <v>0.96</v>
       </c>
       <c r="J31" t="n">
-        <v>0.625</v>
+        <v>0.64</v>
       </c>
       <c r="K31" t="n">
-        <v>1.958</v>
+        <v>1.88</v>
       </c>
       <c r="L31" t="n">
-        <v>1.125</v>
+        <v>1.12</v>
       </c>
       <c r="M31" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="N31" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.583</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.583</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R31" t="n">
-        <v>1.417</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
-        <v>1.125</v>
+        <v>1.12</v>
       </c>
       <c r="T31" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="U31" t="n">
-        <v>0.875</v>
+        <v>0.84</v>
       </c>
       <c r="V31" t="n">
-        <v>1.125</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>0.792</v>
+        <v>0.84</v>
       </c>
       <c r="X31" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.208</v>
+        <v>1.32</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.667</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.725</v>
+        <v>0.733</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="AD31" t="n">
         <v>0.4</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.375</v>
+        <v>0.36</v>
       </c>
       <c r="AG31" t="n">
         <v>0.222</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.583</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.333</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.333</v>
+        <v>2.32</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.321</v>
+        <v>0.328</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>6.82</v>
+        <v>6.782</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.493</v>
+        <v>0.507</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.514</v>
+        <v>0.527</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.967</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.114</v>
+        <v>0.117</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.071</v>
+        <v>1.143</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.169</v>
+        <v>0.168</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.119</v>
+        <v>0.115</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="32">
@@ -5133,40 +5133,40 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>8.893000000000001</v>
+        <v>9.125</v>
       </c>
       <c r="D32" t="n">
-        <v>2.214</v>
+        <v>2.25</v>
       </c>
       <c r="E32" t="n">
-        <v>3.464</v>
+        <v>3.438</v>
       </c>
       <c r="F32" t="n">
-        <v>0.929</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>2.679</v>
+        <v>2.781</v>
       </c>
       <c r="H32" t="n">
-        <v>1.679</v>
+        <v>1.625</v>
       </c>
       <c r="I32" t="n">
-        <v>2.536</v>
+        <v>2.375</v>
       </c>
       <c r="J32" t="n">
-        <v>0.571</v>
+        <v>0.531</v>
       </c>
       <c r="K32" t="n">
-        <v>1.929</v>
+        <v>1.906</v>
       </c>
       <c r="L32" t="n">
-        <v>1.107</v>
+        <v>0.969</v>
       </c>
       <c r="M32" t="n">
-        <v>0.214</v>
+        <v>0.219</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
@@ -5175,114 +5175,114 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.312</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.031</v>
+      </c>
+      <c r="T32" t="n">
+        <v>295</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.143</v>
-      </c>
-      <c r="T32" t="n">
-        <v>258</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.536</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.464</v>
-      </c>
       <c r="X32" t="n">
-        <v>0.214</v>
+        <v>0.219</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.286</v>
+        <v>3.188</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.5</v>
+        <v>4.281</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.73</v>
+        <v>0.745</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.464</v>
+        <v>0.469</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.143</v>
+        <v>1.062</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.406</v>
+        <v>0.441</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.143</v>
+        <v>0.219</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.357</v>
+        <v>0.469</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.179</v>
+        <v>0.156</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.4</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.857</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.343</v>
+        <v>0.357</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>7.759</v>
+        <v>7.795</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.587</v>
+        <v>0.603</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.613</v>
+        <v>0.628</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.146</v>
+        <v>1.171</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.273</v>
+        <v>0.261</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.143</v>
+        <v>1</v>
       </c>
       <c r="AV32" t="n">
         <v>0.203</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.123</v>
+        <v>0.122</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C33" t="n">
-        <v>10.692</v>
+        <v>10.655</v>
       </c>
       <c r="D33" t="n">
-        <v>3.269</v>
+        <v>3.31</v>
       </c>
       <c r="E33" t="n">
-        <v>4.577</v>
+        <v>4.655</v>
       </c>
       <c r="F33" t="n">
-        <v>0.846</v>
+        <v>0.759</v>
       </c>
       <c r="G33" t="n">
-        <v>2.192</v>
+        <v>2.172</v>
       </c>
       <c r="H33" t="n">
-        <v>1.615</v>
+        <v>1.759</v>
       </c>
       <c r="I33" t="n">
-        <v>2.385</v>
+        <v>2.517</v>
       </c>
       <c r="J33" t="n">
-        <v>2.346</v>
+        <v>2.276</v>
       </c>
       <c r="K33" t="n">
-        <v>3.923</v>
+        <v>3.828</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1.862</v>
       </c>
       <c r="M33" t="n">
-        <v>0.769</v>
+        <v>0.793</v>
       </c>
       <c r="N33" t="n">
-        <v>0.5</v>
+        <v>0.448</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.538</v>
+        <v>1.517</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.538</v>
+        <v>1.517</v>
       </c>
       <c r="R33" t="n">
-        <v>1.192</v>
+        <v>1.241</v>
       </c>
       <c r="S33" t="n">
-        <v>2.846</v>
+        <v>3.069</v>
       </c>
       <c r="T33" t="n">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="U33" t="n">
-        <v>0.846</v>
+        <v>1.069</v>
       </c>
       <c r="V33" t="n">
-        <v>2.038</v>
+        <v>1.897</v>
       </c>
       <c r="W33" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>4.448</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5.828</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="AC33" t="n">
         <v>1</v>
       </c>
-      <c r="X33" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>4.231</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.615</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.962</v>
-      </c>
       <c r="AD33" t="n">
-        <v>0.52</v>
+        <v>0.483</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.154</v>
+        <v>0.138</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.385</v>
+        <v>0.345</v>
       </c>
       <c r="AG33" t="n">
         <v>0.4</v>
       </c>
       <c r="AH33" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>0.385</v>
       </c>
-      <c r="AI33" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.417</v>
-      </c>
       <c r="AK33" t="n">
-        <v>0.462</v>
+        <v>0.414</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.269</v>
+        <v>1.276</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.364</v>
+        <v>0.324</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>9.356999999999999</v>
+        <v>9.452</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.67</v>
+        <v>0.652</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.143</v>
+        <v>1.127</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.164</v>
+        <v>0.161</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.239</v>
+        <v>0.258</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.525</v>
+        <v>1.5</v>
       </c>
       <c r="AV33" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AX33" t="n">
         <v>0.193</v>
       </c>
-      <c r="AW33" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0.198</v>
-      </c>
       <c r="AY33" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="34">
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C34" t="n">
-        <v>8.913</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>1.435</v>
+        <v>1.556</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>3.185</v>
       </c>
       <c r="F34" t="n">
-        <v>1.261</v>
+        <v>1.296</v>
       </c>
       <c r="G34" t="n">
-        <v>2.913</v>
+        <v>3.111</v>
       </c>
       <c r="H34" t="n">
-        <v>2.261</v>
+        <v>2.37</v>
       </c>
       <c r="I34" t="n">
-        <v>2.783</v>
+        <v>2.889</v>
       </c>
       <c r="J34" t="n">
-        <v>3.304</v>
+        <v>3.63</v>
       </c>
       <c r="K34" t="n">
-        <v>1.478</v>
+        <v>1.556</v>
       </c>
       <c r="L34" t="n">
-        <v>1.348</v>
+        <v>1.296</v>
       </c>
       <c r="M34" t="n">
-        <v>0.435</v>
+        <v>0.481</v>
       </c>
       <c r="N34" t="n">
-        <v>0.522</v>
+        <v>0.519</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.739</v>
+        <v>1.704</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.739</v>
+        <v>1.704</v>
       </c>
       <c r="R34" t="n">
-        <v>1.478</v>
+        <v>1.519</v>
       </c>
       <c r="S34" t="n">
-        <v>3.261</v>
+        <v>3.222</v>
       </c>
       <c r="T34" t="n">
-        <v>283</v>
+        <v>348</v>
       </c>
       <c r="U34" t="n">
-        <v>1.043</v>
+        <v>1.185</v>
       </c>
       <c r="V34" t="n">
-        <v>1.435</v>
+        <v>1.296</v>
       </c>
       <c r="W34" t="n">
-        <v>0.478</v>
+        <v>0.556</v>
       </c>
       <c r="X34" t="n">
-        <v>0.304</v>
+        <v>0.333</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.217</v>
+        <v>3.37</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.043</v>
+        <v>4.259</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.796</v>
+        <v>0.791</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.391</v>
+        <v>0.407</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.043</v>
+        <v>1.111</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.375</v>
+        <v>0.367</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.148</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.696</v>
+        <v>0.704</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.125</v>
+        <v>0.211</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.261</v>
+        <v>0.37</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.522</v>
+        <v>0.63</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.5</v>
+        <v>0.588</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.391</v>
+        <v>2.481</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.418</v>
+        <v>0.373</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>8.877000000000001</v>
+        <v>9.271000000000001</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.624</v>
+        <v>0.619</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.004</v>
+        <v>1.011</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.196</v>
+        <v>0.184</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.382</v>
+        <v>0.376</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.232</v>
+        <v>0.229</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="AX34" t="n">
         <v>0.094</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.109</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="35">
@@ -5753,10 +5753,10 @@
         <v>0.199</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="AY35" t="n">
         <v>0.024</v>
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C36" t="n">
-        <v>5.833</v>
+        <v>5.682</v>
       </c>
       <c r="D36" t="n">
-        <v>1.833</v>
+        <v>1.818</v>
       </c>
       <c r="E36" t="n">
-        <v>3.333</v>
+        <v>3.227</v>
       </c>
       <c r="F36" t="n">
-        <v>0.444</v>
+        <v>0.455</v>
       </c>
       <c r="G36" t="n">
-        <v>1.222</v>
+        <v>1.227</v>
       </c>
       <c r="H36" t="n">
-        <v>0.833</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>1.778</v>
+        <v>1.545</v>
       </c>
       <c r="J36" t="n">
-        <v>1.111</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>2.167</v>
+        <v>2.227</v>
       </c>
       <c r="L36" t="n">
-        <v>0.667</v>
+        <v>0.773</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0.864</v>
       </c>
       <c r="N36" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.722</v>
+        <v>0.909</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.722</v>
+        <v>0.909</v>
       </c>
       <c r="R36" t="n">
-        <v>1.611</v>
+        <v>1.455</v>
       </c>
       <c r="S36" t="n">
-        <v>1.278</v>
+        <v>1.273</v>
       </c>
       <c r="T36" t="n">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>0.833</v>
+        <v>0.773</v>
       </c>
       <c r="W36" t="n">
-        <v>0.556</v>
+        <v>0.545</v>
       </c>
       <c r="X36" t="n">
-        <v>0.333</v>
+        <v>0.318</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.056</v>
+        <v>1.955</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.444</v>
+        <v>3.182</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.597</v>
+        <v>0.614</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.556</v>
+        <v>0.455</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.389</v>
+        <v>1.273</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.4</v>
+        <v>0.357</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.056</v>
+        <v>0.091</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.278</v>
+        <v>0.318</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.2</v>
+        <v>0.286</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.056</v>
+        <v>0.091</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.611</v>
+        <v>0.591</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.091</v>
+        <v>0.154</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.389</v>
+        <v>0.364</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.611</v>
+        <v>0.636</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.636</v>
+        <v>0.571</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>6.06</v>
+        <v>6.044</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.549</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.546</v>
+        <v>0.553</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.963</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.119</v>
+        <v>0.15</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.183</v>
+        <v>0.153</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.538</v>
+        <v>1.1</v>
       </c>
       <c r="AV36" t="n">
         <v>0.17</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.045</v>
+        <v>0.053</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.149</v>
+        <v>0.154</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.036</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="37">
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C37" t="n">
-        <v>14.864</v>
+        <v>14.167</v>
       </c>
       <c r="D37" t="n">
-        <v>2.682</v>
+        <v>2.667</v>
       </c>
       <c r="E37" t="n">
-        <v>5.409</v>
+        <v>5.25</v>
       </c>
       <c r="F37" t="n">
-        <v>2.227</v>
+        <v>2.083</v>
       </c>
       <c r="G37" t="n">
-        <v>5.364</v>
+        <v>5.208</v>
       </c>
       <c r="H37" t="n">
-        <v>2.818</v>
+        <v>2.583</v>
       </c>
       <c r="I37" t="n">
-        <v>3.227</v>
+        <v>2.958</v>
       </c>
       <c r="J37" t="n">
-        <v>3.864</v>
+        <v>3.833</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>2.042</v>
       </c>
       <c r="L37" t="n">
-        <v>0.591</v>
+        <v>0.583</v>
       </c>
       <c r="M37" t="n">
-        <v>1.182</v>
+        <v>1.208</v>
       </c>
       <c r="N37" t="n">
-        <v>0.318</v>
+        <v>0.333</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.364</v>
+        <v>1.375</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.364</v>
+        <v>1.375</v>
       </c>
       <c r="R37" t="n">
-        <v>1.091</v>
+        <v>1.125</v>
       </c>
       <c r="S37" t="n">
-        <v>3.455</v>
+        <v>3.25</v>
       </c>
       <c r="T37" t="n">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="U37" t="n">
-        <v>2.591</v>
+        <v>2.542</v>
       </c>
       <c r="V37" t="n">
-        <v>1.682</v>
+        <v>1.625</v>
       </c>
       <c r="W37" t="n">
-        <v>0.909</v>
+        <v>0.833</v>
       </c>
       <c r="X37" t="n">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.636</v>
+        <v>4.417</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.818</v>
+        <v>5.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.797</v>
+        <v>0.803</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.591</v>
+        <v>1.542</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.286</v>
+        <v>0.27</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.409</v>
+        <v>0.417</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.227</v>
+        <v>1.167</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.5</v>
+        <v>0.458</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.864</v>
+        <v>0.792</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.579</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.727</v>
+        <v>1.625</v>
       </c>
       <c r="AL37" t="n">
-        <v>4.5</v>
+        <v>4.417</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.384</v>
+        <v>0.368</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>13.556</v>
+        <v>13.135</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.61</v>
+        <v>0.602</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.096</v>
+        <v>1.079</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.262</v>
+        <v>0.247</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.833</v>
+        <v>2.788</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.282</v>
+        <v>0.276</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.102</v>
+        <v>0.105</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.137</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="38">
@@ -6087,156 +6087,156 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C38" t="n">
-        <v>8.52</v>
+        <v>8.724</v>
       </c>
       <c r="D38" t="n">
-        <v>2.2</v>
+        <v>2.241</v>
       </c>
       <c r="E38" t="n">
-        <v>4.12</v>
+        <v>4.103</v>
       </c>
       <c r="F38" t="n">
-        <v>0.88</v>
+        <v>0.966</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32</v>
+        <v>2.414</v>
       </c>
       <c r="H38" t="n">
-        <v>1.48</v>
+        <v>1.345</v>
       </c>
       <c r="I38" t="n">
-        <v>1.88</v>
+        <v>1.724</v>
       </c>
       <c r="J38" t="n">
-        <v>2.68</v>
+        <v>2.724</v>
       </c>
       <c r="K38" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="M38" t="n">
-        <v>0.52</v>
+        <v>0.586</v>
       </c>
       <c r="N38" t="n">
-        <v>0.72</v>
+        <v>0.759</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.2</v>
+        <v>1.276</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.2</v>
+        <v>1.276</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S38" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="T38" t="n">
-        <v>256</v>
+        <v>311</v>
       </c>
       <c r="U38" t="n">
-        <v>1.04</v>
+        <v>1.138</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.138</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.069</v>
       </c>
       <c r="X38" t="n">
-        <v>0.48</v>
+        <v>0.483</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.84</v>
+        <v>2.862</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>3.966</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.71</v>
+        <v>0.722</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.76</v>
+        <v>0.655</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.72</v>
+        <v>1.621</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.442</v>
+        <v>0.404</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.08</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.28</v>
+        <v>0.241</v>
       </c>
       <c r="AG38" t="n">
         <v>0.286</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.2</v>
+        <v>0.172</v>
       </c>
       <c r="AI38" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.759</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>8.552</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="AQ38" t="n">
         <v>0.6</v>
       </c>
-      <c r="AJ38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>8.467000000000001</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.586</v>
-      </c>
       <c r="AR38" t="n">
-        <v>1.006</v>
+        <v>1.02</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.142</v>
+        <v>0.149</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.23</v>
+        <v>0.206</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.233</v>
+        <v>2.135</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="AX38" t="n">
         <v>0.096</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="39">
@@ -6246,16 +6246,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C39" t="n">
-        <v>4.652</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>1.957</v>
+        <v>2.12</v>
       </c>
       <c r="E39" t="n">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6264,79 +6264,79 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.739</v>
+        <v>0.76</v>
       </c>
       <c r="I39" t="n">
-        <v>1.913</v>
+        <v>1.84</v>
       </c>
       <c r="J39" t="n">
-        <v>0.826</v>
+        <v>0.8</v>
       </c>
       <c r="K39" t="n">
-        <v>1.913</v>
+        <v>1.92</v>
       </c>
       <c r="L39" t="n">
-        <v>1.783</v>
+        <v>1.76</v>
       </c>
       <c r="M39" t="n">
-        <v>0.478</v>
+        <v>0.48</v>
       </c>
       <c r="N39" t="n">
-        <v>0.739</v>
+        <v>0.72</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.652</v>
+        <v>0.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.652</v>
+        <v>0.64</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S39" t="n">
-        <v>1.696</v>
+        <v>1.68</v>
       </c>
       <c r="T39" t="n">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="U39" t="n">
-        <v>0.609</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V39" t="n">
-        <v>0.609</v>
+        <v>0.88</v>
       </c>
       <c r="W39" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="X39" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.261</v>
+        <v>2.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.913</v>
+        <v>3.96</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.578</v>
+        <v>0.606</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.391</v>
+        <v>0.44</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.913</v>
+        <v>1</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.429</v>
+        <v>0.44</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.217</v>
+        <v>0.2</v>
       </c>
       <c r="AG39" t="n">
         <v>0.2</v>
@@ -6361,41 +6361,41 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>4.624</v>
+        <v>4.77</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.625</v>
+        <v>0.639</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.586</v>
+        <v>0.605</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.006</v>
+        <v>1.048</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.141</v>
+        <v>0.134</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.236</v>
+        <v>0.229</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.267</v>
+        <v>1.25</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.134</v>
+        <v>0.139</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="40">
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C40" t="n">
-        <v>7.792</v>
+        <v>7.357</v>
       </c>
       <c r="D40" t="n">
-        <v>1.542</v>
+        <v>1.393</v>
       </c>
       <c r="E40" t="n">
-        <v>2.667</v>
+        <v>2.464</v>
       </c>
       <c r="F40" t="n">
-        <v>1.083</v>
+        <v>1.071</v>
       </c>
       <c r="G40" t="n">
-        <v>3.208</v>
+        <v>3.286</v>
       </c>
       <c r="H40" t="n">
-        <v>1.458</v>
+        <v>1.357</v>
       </c>
       <c r="I40" t="n">
-        <v>1.792</v>
+        <v>1.643</v>
       </c>
       <c r="J40" t="n">
-        <v>3.083</v>
+        <v>2.857</v>
       </c>
       <c r="K40" t="n">
-        <v>1.042</v>
+        <v>0.964</v>
       </c>
       <c r="L40" t="n">
-        <v>0.917</v>
+        <v>0.857</v>
       </c>
       <c r="M40" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="N40" t="n">
-        <v>0.375</v>
+        <v>0.321</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0.893</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0.893</v>
       </c>
       <c r="R40" t="n">
-        <v>1.833</v>
+        <v>1.821</v>
       </c>
       <c r="S40" t="n">
-        <v>1.458</v>
+        <v>1.393</v>
       </c>
       <c r="T40" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="U40" t="n">
-        <v>1.458</v>
+        <v>1.393</v>
       </c>
       <c r="V40" t="n">
-        <v>0.958</v>
+        <v>0.821</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="X40" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.458</v>
+        <v>2.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.958</v>
+        <v>2.714</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.831</v>
+        <v>0.829</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.292</v>
+        <v>0.286</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.917</v>
+        <v>0.893</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.318</v>
+        <v>0.32</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.25</v>
+        <v>0.214</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="AG40" t="n">
         <v>0.429</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.167</v>
+        <v>0.179</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.333</v>
+        <v>0.321</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.917</v>
+        <v>0.893</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.875</v>
+        <v>2.964</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.319</v>
+        <v>0.301</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>7.663</v>
+        <v>7.366</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.539</v>
+        <v>0.522</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.585</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.017</v>
+        <v>0.999</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.13</v>
+        <v>0.121</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.248</v>
+        <v>0.236</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.083</v>
+        <v>3.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.101</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="41">
@@ -6704,7 +6704,7 @@
         <v>2</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.663</v>
+        <v>0.662</v>
       </c>
       <c r="AW41" t="n">
         <v>0</v>
@@ -6713,584 +6713,584 @@
         <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#24 M. COSTELLO (Per Game)</t>
+          <t>#23 A. CÁRDENAS (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>7.68</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.52</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.52</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="S42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>241</v>
+        <v>-7</v>
       </c>
       <c r="U42" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.634</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
         <v>1</v>
       </c>
-      <c r="AJ42" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
-        <v>6.976</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.101</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0.075</v>
-      </c>
       <c r="AT42" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.769</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.178</v>
+        <v>0.196</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#32 I. NOGUÉS (Per Game)</t>
+          <t>#24 M. COSTELLO (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C43" t="n">
-        <v>0.588</v>
+        <v>7.586</v>
       </c>
       <c r="D43" t="n">
-        <v>0.118</v>
+        <v>1.414</v>
       </c>
       <c r="E43" t="n">
-        <v>0.588</v>
+        <v>2.138</v>
       </c>
       <c r="F43" t="n">
-        <v>0.059</v>
+        <v>1.379</v>
       </c>
       <c r="G43" t="n">
-        <v>0.353</v>
+        <v>3.621</v>
       </c>
       <c r="H43" t="n">
-        <v>0.176</v>
+        <v>0.621</v>
       </c>
       <c r="I43" t="n">
-        <v>0.235</v>
+        <v>1.31</v>
       </c>
       <c r="J43" t="n">
-        <v>0.706</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>2.621</v>
       </c>
       <c r="L43" t="n">
-        <v>0.529</v>
+        <v>1.483</v>
       </c>
       <c r="M43" t="n">
-        <v>0.529</v>
+        <v>0.828</v>
       </c>
       <c r="N43" t="n">
-        <v>0.118</v>
+        <v>0.897</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.235</v>
+        <v>0.517</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.235</v>
+        <v>0.517</v>
       </c>
       <c r="R43" t="n">
-        <v>1.765</v>
+        <v>1.759</v>
       </c>
       <c r="S43" t="n">
-        <v>0.412</v>
+        <v>1.345</v>
       </c>
       <c r="T43" t="n">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="U43" t="n">
-        <v>0.235</v>
+        <v>0.862</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.759</v>
       </c>
       <c r="W43" t="n">
-        <v>0.176</v>
+        <v>0.828</v>
       </c>
       <c r="X43" t="n">
-        <v>0.118</v>
+        <v>0.379</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.294</v>
+        <v>1.724</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.529</v>
+        <v>2.655</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.556</v>
+        <v>0.649</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.235</v>
+        <v>0.621</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.059</v>
+        <v>0.172</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.059</v>
+        <v>0.448</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.176</v>
+        <v>0.862</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.333</v>
+        <v>0.52</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>0.931</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.176</v>
+        <v>2.759</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>1.28</v>
+        <v>6.852</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.219</v>
+        <v>0.605</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.282</v>
+        <v>0.599</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.46</v>
+        <v>1.107</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.184</v>
+        <v>0.075</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.188</v>
+        <v>0.108</v>
       </c>
       <c r="AU43" t="n">
-        <v>3</v>
+        <v>1.933</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.175</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.092</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#77 Y. SIMA (Per Game)</t>
+          <t>#32 I. NOGUÉS (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C44" t="n">
-        <v>2.824</v>
+        <v>0.571</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="E44" t="n">
-        <v>1.529</v>
+        <v>0.571</v>
       </c>
       <c r="F44" t="n">
-        <v>0.118</v>
+        <v>0.048</v>
       </c>
       <c r="G44" t="n">
-        <v>0.588</v>
+        <v>0.333</v>
       </c>
       <c r="H44" t="n">
-        <v>0.588</v>
+        <v>0.143</v>
       </c>
       <c r="I44" t="n">
-        <v>1.059</v>
+        <v>0.19</v>
       </c>
       <c r="J44" t="n">
-        <v>0.294</v>
+        <v>0.667</v>
       </c>
       <c r="K44" t="n">
-        <v>0.882</v>
+        <v>0.952</v>
       </c>
       <c r="L44" t="n">
-        <v>0.824</v>
+        <v>0.429</v>
       </c>
       <c r="M44" t="n">
-        <v>0.176</v>
+        <v>0.571</v>
       </c>
       <c r="N44" t="n">
-        <v>0.412</v>
+        <v>0.095</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.471</v>
+        <v>0.286</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.471</v>
+        <v>0.286</v>
       </c>
       <c r="R44" t="n">
-        <v>1.294</v>
+        <v>1.667</v>
       </c>
       <c r="S44" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="T44" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="U44" t="n">
-        <v>0.353</v>
+        <v>0.286</v>
       </c>
       <c r="V44" t="n">
-        <v>0.882</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.059</v>
+        <v>0.143</v>
       </c>
       <c r="X44" t="n">
-        <v>0.059</v>
+        <v>0.095</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.471</v>
+        <v>0.286</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.353</v>
+        <v>0.476</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.176</v>
+        <v>0.19</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.059</v>
+        <v>0.095</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.588</v>
+        <v>0.143</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>3.054</v>
+        <v>1.274</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.528</v>
+        <v>0.237</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.546</v>
+        <v>0.289</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.924</v>
+        <v>0.448</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.154</v>
+        <v>0.224</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.278</v>
+        <v>0.158</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.625</v>
+        <v>2.333</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.164</v>
+        <v>0.081</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.106</v>
+        <v>0.066</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.116</v>
+        <v>0.15</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#77 Y. SIMA (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>2.905</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.952</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1.619</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>0.905</v>
       </c>
       <c r="L45" t="n">
-        <v>1.714</v>
+        <v>0.857</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.476</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.464</v>
+        <v>0.524</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="R45" t="n">
-        <v>0.036</v>
+        <v>1.286</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.381</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.619</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -7305,51 +7305,51 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>3.253</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>0.893</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="46">
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2.031</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.656</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7401,19 +7401,19 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
         <v>0</v>
@@ -7518,118 +7518,118 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C47" t="n">
-        <v>94.179</v>
+        <v>94.09399999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>21.179</v>
+        <v>21.75</v>
       </c>
       <c r="E47" t="n">
-        <v>37.286</v>
+        <v>37.562</v>
       </c>
       <c r="F47" t="n">
-        <v>11.929</v>
+        <v>11.719</v>
       </c>
       <c r="G47" t="n">
-        <v>32.714</v>
+        <v>32.594</v>
       </c>
       <c r="H47" t="n">
-        <v>16.036</v>
+        <v>15.438</v>
       </c>
       <c r="I47" t="n">
-        <v>22.464</v>
+        <v>21.625</v>
       </c>
       <c r="J47" t="n">
         <v>20.75</v>
       </c>
       <c r="K47" t="n">
-        <v>26.321</v>
+        <v>26.219</v>
       </c>
       <c r="L47" t="n">
-        <v>14.464</v>
+        <v>14.125</v>
       </c>
       <c r="M47" t="n">
-        <v>7.821</v>
+        <v>7.844</v>
       </c>
       <c r="N47" t="n">
-        <v>6.464</v>
+        <v>6.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>12.036</v>
+        <v>12.281</v>
       </c>
       <c r="Q47" t="n">
-        <v>11.571</v>
+        <v>11.812</v>
       </c>
       <c r="R47" t="n">
-        <v>19.321</v>
+        <v>19.375</v>
       </c>
       <c r="S47" t="n">
-        <v>22.357</v>
+        <v>22.094</v>
       </c>
       <c r="T47" t="n">
-        <v>3295</v>
+        <v>3747</v>
       </c>
       <c r="U47" t="n">
-        <v>13.786</v>
+        <v>13.75</v>
       </c>
       <c r="V47" t="n">
-        <v>13.107</v>
+        <v>12.625</v>
       </c>
       <c r="W47" t="n">
-        <v>8.429</v>
+        <v>8.718999999999999</v>
       </c>
       <c r="X47" t="n">
-        <v>4.536</v>
+        <v>4.656</v>
       </c>
       <c r="Y47" t="n">
-        <v>30.536</v>
+        <v>30.438</v>
       </c>
       <c r="Z47" t="n">
-        <v>42.179</v>
+        <v>41.719</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.724</v>
+        <v>0.73</v>
       </c>
       <c r="AB47" t="n">
-        <v>4.714</v>
+        <v>4.625</v>
       </c>
       <c r="AC47" t="n">
-        <v>11.714</v>
+        <v>11.594</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.402</v>
+        <v>0.399</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.964</v>
+        <v>2.125</v>
       </c>
       <c r="AF47" t="n">
-        <v>5.857</v>
+        <v>5.875</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.335</v>
+        <v>0.362</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.25</v>
+        <v>3.062</v>
       </c>
       <c r="AI47" t="n">
-        <v>7.893</v>
+        <v>7.719</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.412</v>
+        <v>0.397</v>
       </c>
       <c r="AK47" t="n">
-        <v>8.679</v>
+        <v>8.656000000000001</v>
       </c>
       <c r="AL47" t="n">
-        <v>24.821</v>
+        <v>24.875</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
@@ -7637,25 +7637,25 @@
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>91.92</v>
+        <v>91.952</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.589</v>
+        <v>0.591</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.025</v>
+        <v>1.023</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.131</v>
+        <v>0.134</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.229</v>
+        <v>0.22</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.724</v>
+        <v>1.69</v>
       </c>
       <c r="AV47" t="n">
         <v>0.2</v>
@@ -7677,118 +7677,118 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>82.5</v>
+        <v>83.46899999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>19.75</v>
+        <v>20</v>
       </c>
       <c r="E48" t="n">
-        <v>37</v>
+        <v>37.312</v>
       </c>
       <c r="F48" t="n">
-        <v>9.856999999999999</v>
+        <v>9.843999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>30.464</v>
+        <v>30.125</v>
       </c>
       <c r="H48" t="n">
-        <v>13.429</v>
+        <v>13.938</v>
       </c>
       <c r="I48" t="n">
-        <v>17.643</v>
+        <v>18.25</v>
       </c>
       <c r="J48" t="n">
         <v>16.75</v>
       </c>
       <c r="K48" t="n">
-        <v>23.964</v>
+        <v>23.75</v>
       </c>
       <c r="L48" t="n">
-        <v>11.25</v>
+        <v>11.188</v>
       </c>
       <c r="M48" t="n">
-        <v>6.286</v>
+        <v>6.438</v>
       </c>
       <c r="N48" t="n">
-        <v>6.429</v>
+        <v>6.469</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>13.643</v>
+        <v>13.656</v>
       </c>
       <c r="Q48" t="n">
-        <v>12.75</v>
+        <v>12.719</v>
       </c>
       <c r="R48" t="n">
-        <v>22.393</v>
+        <v>22.094</v>
       </c>
       <c r="S48" t="n">
-        <v>19.179</v>
+        <v>19.281</v>
       </c>
       <c r="T48" t="n">
-        <v>2471</v>
+        <v>2870</v>
       </c>
       <c r="U48" t="n">
-        <v>9.214</v>
+        <v>9.625</v>
       </c>
       <c r="V48" t="n">
-        <v>9.821</v>
+        <v>9.561999999999999</v>
       </c>
       <c r="W48" t="n">
-        <v>6.071</v>
+        <v>6.219</v>
       </c>
       <c r="X48" t="n">
-        <v>3.321</v>
+        <v>3.375</v>
       </c>
       <c r="Y48" t="n">
-        <v>25.929</v>
+        <v>26.781</v>
       </c>
       <c r="Z48" t="n">
-        <v>35.536</v>
+        <v>36.781</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.071</v>
+        <v>5.031</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.286</v>
+        <v>12.125</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.413</v>
+        <v>0.415</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.179</v>
+        <v>2.125</v>
       </c>
       <c r="AF48" t="n">
-        <v>6.821</v>
+        <v>6.656</v>
       </c>
       <c r="AG48" t="n">
         <v>0.319</v>
       </c>
       <c r="AH48" t="n">
-        <v>3.107</v>
+        <v>3.062</v>
       </c>
       <c r="AI48" t="n">
-        <v>8.071</v>
+        <v>8.281000000000001</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.385</v>
+        <v>0.37</v>
       </c>
       <c r="AK48" t="n">
-        <v>6.75</v>
+        <v>6.781</v>
       </c>
       <c r="AL48" t="n">
-        <v>22.393</v>
+        <v>21.844</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.301</v>
+        <v>0.31</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
@@ -7796,34 +7796,34 @@
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>88.87</v>
+        <v>89.124</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.512</v>
+        <v>0.516</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.548</v>
+        <v>0.553</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.928</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.199</v>
+        <v>0.207</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.228</v>
+        <v>1.227</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.193</v>
+        <v>0.194</v>
       </c>
       <c r="AW48" t="n">
         <v>0.059</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Valencia Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Valencia Basket.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2490.48</v>
+        <v>2647.32</v>
       </c>
       <c r="C2" t="n">
-        <v>2492.22</v>
+        <v>2646.300000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>120.8159793276677</v>
+        <v>121.6037486301628</v>
       </c>
       <c r="E2" t="n">
-        <v>107.1735240067089</v>
+        <v>106.903979140687</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5605790645879732</v>
+        <v>0.5644351464435147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1335608058508469</v>
+        <v>0.1308396829061803</v>
       </c>
       <c r="H2" t="n">
-        <v>0.372937293729373</v>
+        <v>0.3685446009389671</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2200445434298441</v>
+        <v>0.2175732217573222</v>
       </c>
       <c r="J2" t="n">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="K2" t="n">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="L2" t="n">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="M2" t="n">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="N2" t="n">
-        <v>974</v>
+        <v>1038</v>
       </c>
       <c r="O2" t="n">
-        <v>1335</v>
+        <v>1415</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5946547884187082</v>
+        <v>0.5920502092050209</v>
       </c>
       <c r="Q2" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="R2" t="n">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1652561247216036</v>
+        <v>0.1652719665271966</v>
       </c>
       <c r="T2" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="U2" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08374164810690424</v>
+        <v>0.08619246861924686</v>
       </c>
       <c r="W2" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="X2" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.110022271714922</v>
+        <v>0.1096234309623431</v>
       </c>
       <c r="Z2" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="AA2" t="n">
-        <v>796</v>
+        <v>840</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3545657015590201</v>
+        <v>0.3514644351464435</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7295880149812735</v>
+        <v>0.7335689045936395</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.398921832884097</v>
+        <v>0.4025316455696202</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3617021276595745</v>
+        <v>0.3640776699029126</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3967611336032389</v>
+        <v>0.3969465648854962</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3479899497487437</v>
+        <v>0.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.459176029962547</v>
+        <v>1.467137809187279</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.723404255319149</v>
+        <v>0.7281553398058253</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.078619367209971</v>
+        <v>1.083484573502722</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.006864988558352</v>
+        <v>1.023706896551724</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8938053097345132</v>
+        <v>0.9065817409766455</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.87248322147651</v>
+        <v>1.872611464968153</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.689567430025445</v>
+        <v>1.718137254901961</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.712468193384224</v>
+        <v>5.857843137254902</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.402035623409669</v>
+        <v>7.575980392156863</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.82749999999999</v>
+        <v>77.86235294117647</v>
       </c>
       <c r="C3" t="n">
-        <v>77.88187500000001</v>
+        <v>77.8323529411765</v>
       </c>
       <c r="D3" t="n">
-        <v>120.8159793276677</v>
+        <v>121.6037486301628</v>
       </c>
       <c r="E3" t="n">
-        <v>107.1735240067089</v>
+        <v>106.903979140687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5605790645879732</v>
+        <v>0.5644351464435146</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1335608058508469</v>
+        <v>0.1308396829061803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.372937293729373</v>
+        <v>0.3685446009389672</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2200445434298441</v>
+        <v>0.2175732217573222</v>
       </c>
       <c r="J3" t="n">
-        <v>13.75</v>
+        <v>13.97058823529412</v>
       </c>
       <c r="K3" t="n">
-        <v>12.625</v>
+        <v>12.55882352941176</v>
       </c>
       <c r="L3" t="n">
-        <v>8.71875</v>
+        <v>8.647058823529411</v>
       </c>
       <c r="M3" t="n">
-        <v>11.8125</v>
+        <v>11.55882352941176</v>
       </c>
       <c r="N3" t="n">
-        <v>30.4375</v>
+        <v>30.52941176470588</v>
       </c>
       <c r="O3" t="n">
-        <v>41.71875</v>
+        <v>41.61764705882353</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5946547884187082</v>
+        <v>0.5920502092050209</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.625</v>
+        <v>4.676470588235294</v>
       </c>
       <c r="R3" t="n">
-        <v>11.59375</v>
+        <v>11.61764705882353</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1652561247216036</v>
+        <v>0.1652719665271966</v>
       </c>
       <c r="T3" t="n">
-        <v>2.125</v>
+        <v>2.205882352941177</v>
       </c>
       <c r="U3" t="n">
-        <v>5.875</v>
+        <v>6.058823529411764</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08374164810690424</v>
+        <v>0.08619246861924686</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0625</v>
+        <v>3.058823529411764</v>
       </c>
       <c r="X3" t="n">
-        <v>7.71875</v>
+        <v>7.705882352941177</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.110022271714922</v>
+        <v>0.1096234309623431</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.65625</v>
+        <v>8.647058823529411</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.875</v>
+        <v>24.70588235294118</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3545657015590201</v>
+        <v>0.3514644351464435</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7295880149812735</v>
+        <v>0.7335689045936397</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.398921832884097</v>
+        <v>0.4025316455696203</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3617021276595745</v>
+        <v>0.3640776699029127</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3967611336032389</v>
+        <v>0.3969465648854961</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3479899497487437</v>
+        <v>0.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.459176029962547</v>
+        <v>1.467137809187279</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.723404255319149</v>
+        <v>0.7281553398058254</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.078619367209971</v>
+        <v>1.083484573502722</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.006864988558352</v>
+        <v>1.023706896551724</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8938053097345132</v>
+        <v>0.9065817409766453</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.87248322147651</v>
+        <v>1.872611464968153</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.689567430025445</v>
+        <v>1.718137254901961</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.712468193384224</v>
+        <v>5.857843137254902</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.402035623409669</v>
+        <v>7.575980392156862</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2493.96</v>
+        <v>2645.28</v>
       </c>
       <c r="C4" t="n">
-        <v>2492.22</v>
+        <v>2646.300000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>107.1735240067089</v>
+        <v>106.903979140687</v>
       </c>
       <c r="E4" t="n">
-        <v>120.8159793276677</v>
+        <v>121.6037486301628</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5155236329935126</v>
+        <v>0.5154954168485377</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1532279555112975</v>
+        <v>0.1534249474255029</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2990810359231412</v>
+        <v>0.2974882260596546</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2066728452270621</v>
+        <v>0.2038411174159755</v>
       </c>
       <c r="J4" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="K4" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="L4" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="M4" t="n">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="N4" t="n">
-        <v>857</v>
+        <v>901</v>
       </c>
       <c r="O4" t="n">
-        <v>1177</v>
+        <v>1233</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5454124189063948</v>
+        <v>0.5381929288520296</v>
       </c>
       <c r="Q4" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="R4" t="n">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1797961075069509</v>
+        <v>0.1837625491051942</v>
       </c>
       <c r="T4" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="U4" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09870250231696015</v>
+        <v>0.1008293321693584</v>
       </c>
       <c r="W4" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="X4" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1227988878591288</v>
+        <v>0.122217372326495</v>
       </c>
       <c r="Z4" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="AA4" t="n">
-        <v>699</v>
+        <v>738</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3239110287303059</v>
+        <v>0.3221300742034046</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7281223449447749</v>
+        <v>0.7307380373073804</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4149484536082474</v>
+        <v>0.4180522565320665</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3192488262910798</v>
+        <v>0.316017316017316</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.369811320754717</v>
+        <v>0.3642857142857143</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3104434907010014</v>
+        <v>0.3116531165311653</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.45624468988955</v>
+        <v>1.461476074614761</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6384976525821596</v>
+        <v>0.6320346320346321</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9802904564315352</v>
+        <v>0.9783889980353635</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7837150127226463</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8547486033519553</v>
+        <v>0.8654353562005277</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.842592592592593</v>
+        <v>1.866071428571429</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.226544622425629</v>
+        <v>1.193965517241379</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.938215102974828</v>
+        <v>4.9375</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.164759725400458</v>
+        <v>6.131465517241379</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.93624999999999</v>
+        <v>77.80235294117647</v>
       </c>
       <c r="C5" t="n">
-        <v>77.88187500000001</v>
+        <v>77.8323529411765</v>
       </c>
       <c r="D5" t="n">
-        <v>107.1735240067089</v>
+        <v>106.903979140687</v>
       </c>
       <c r="E5" t="n">
-        <v>120.8159793276677</v>
+        <v>121.6037486301628</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5155236329935126</v>
+        <v>0.5154954168485378</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1532279555112975</v>
+        <v>0.1534249474255029</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2990810359231412</v>
+        <v>0.2974882260596546</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2066728452270621</v>
+        <v>0.2038411174159756</v>
       </c>
       <c r="J5" t="n">
-        <v>9.625</v>
+        <v>9.5</v>
       </c>
       <c r="K5" t="n">
-        <v>9.5625</v>
+        <v>9.647058823529411</v>
       </c>
       <c r="L5" t="n">
-        <v>6.21875</v>
+        <v>6.147058823529412</v>
       </c>
       <c r="M5" t="n">
-        <v>12.71875</v>
+        <v>12.73529411764706</v>
       </c>
       <c r="N5" t="n">
-        <v>26.78125</v>
+        <v>26.5</v>
       </c>
       <c r="O5" t="n">
-        <v>36.78125</v>
+        <v>36.26470588235294</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5454124189063948</v>
+        <v>0.5381929288520297</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.03125</v>
+        <v>5.176470588235294</v>
       </c>
       <c r="R5" t="n">
-        <v>12.125</v>
+        <v>12.38235294117647</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1797961075069509</v>
+        <v>0.1837625491051943</v>
       </c>
       <c r="T5" t="n">
-        <v>2.125</v>
+        <v>2.147058823529412</v>
       </c>
       <c r="U5" t="n">
-        <v>6.65625</v>
+        <v>6.794117647058823</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09870250231696015</v>
+        <v>0.1008293321693584</v>
       </c>
       <c r="W5" t="n">
-        <v>3.0625</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>8.28125</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1227988878591288</v>
+        <v>0.122217372326495</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.78125</v>
+        <v>6.764705882352941</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.84375</v>
+        <v>21.70588235294118</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3239110287303059</v>
+        <v>0.3221300742034047</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7281223449447749</v>
+        <v>0.7307380373073804</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4149484536082474</v>
+        <v>0.4180522565320665</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3192488262910798</v>
+        <v>0.316017316017316</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.369811320754717</v>
+        <v>0.3642857142857143</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3104434907010014</v>
+        <v>0.3116531165311653</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45624468988955</v>
+        <v>1.461476074614761</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6384976525821596</v>
+        <v>0.6320346320346321</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9802904564315352</v>
+        <v>0.9783889980353635</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7837150127226463</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8547486033519553</v>
+        <v>0.8654353562005277</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.842592592592593</v>
+        <v>1.866071428571429</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.226544622425629</v>
+        <v>1.193965517241379</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.938215102974828</v>
+        <v>4.9375</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.164759725400458</v>
+        <v>6.131465517241379</v>
       </c>
     </row>
     <row r="7">
@@ -1419,144 +1419,144 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H8" t="n">
         <v>43</v>
       </c>
       <c r="I8" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K8" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L8" t="n">
+        <v>17</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N8" t="n">
         <v>16</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>39</v>
+      </c>
+      <c r="R8" t="n">
+        <v>56</v>
+      </c>
+      <c r="S8" t="n">
+        <v>61</v>
+      </c>
+      <c r="T8" t="n">
+        <v>277</v>
+      </c>
+      <c r="U8" t="n">
+        <v>54</v>
+      </c>
+      <c r="V8" t="n">
+        <v>39</v>
+      </c>
+      <c r="W8" t="n">
+        <v>44</v>
+      </c>
+      <c r="X8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>73</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="n">
         <v>21</v>
       </c>
-      <c r="N8" t="n">
-        <v>14</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>38</v>
-      </c>
-      <c r="R8" t="n">
-        <v>55</v>
-      </c>
-      <c r="S8" t="n">
-        <v>58</v>
-      </c>
-      <c r="T8" t="n">
-        <v>253</v>
-      </c>
-      <c r="U8" t="n">
-        <v>51</v>
-      </c>
-      <c r="V8" t="n">
-        <v>35</v>
-      </c>
-      <c r="W8" t="n">
-        <v>41</v>
-      </c>
-      <c r="X8" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>69</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>93</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>19</v>
-      </c>
       <c r="AD8" t="n">
-        <v>0.579</v>
+        <v>0.571</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.345</v>
+        <v>0.353</v>
       </c>
       <c r="AH8" t="n">
         <v>12</v>
       </c>
       <c r="AI8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.343</v>
+        <v>0.333</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.319</v>
+        <v>0.331</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>555:10</t>
+          <t>597:44</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>303.32</v>
+        <v>326.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.504</v>
+        <v>0.513</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.541</v>
+        <v>0.545</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.946</v>
+        <v>0.96</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.178</v>
+        <v>0.163</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.5</v>
+        <v>1.513</v>
       </c>
       <c r="AV8" t="n">
         <v>0.238</v>
@@ -1565,10 +1565,10 @@
         <v>0.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="9">
@@ -1578,22 +1578,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H9" t="n">
         <v>22</v>
@@ -1602,16 +1602,16 @@
         <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K9" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L9" t="n">
         <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N9" t="n">
         <v>17</v>
@@ -1620,58 +1620,58 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T9" t="n">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="U9" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="V9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="Z9" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.723</v>
+        <v>0.736</v>
       </c>
       <c r="AB9" t="n">
         <v>22</v>
       </c>
       <c r="AC9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="AH9" t="n">
         <v>9</v>
@@ -1683,51 +1683,51 @@
         <v>0.429</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.392</v>
+        <v>0.411</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>489:40</t>
+          <t>526:34</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>247.2</v>
+        <v>264.2</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.595</v>
+        <v>0.611</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.61</v>
+        <v>0.624</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.048</v>
+        <v>1.06</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.142</v>
+        <v>0.151</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.111</v>
+        <v>0.104</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.571</v>
+        <v>1.45</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.041</v>
+        <v>0.038</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.166</v>
+        <v>0.16</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="10">
@@ -1877,7 +1877,7 @@
         <v>1.143</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="AW10" t="n">
         <v>0.068</v>
@@ -1886,7 +1886,7 @@
         <v>0.115</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="11">
@@ -2039,13 +2039,13 @@
         <v>0.203</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AX11" t="n">
         <v>0.122</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="12">
@@ -2055,22 +2055,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H12" t="n">
         <v>51</v>
@@ -2079,43 +2079,43 @@
         <v>73</v>
       </c>
       <c r="J12" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K12" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="T12" t="n">
-        <v>483</v>
+        <v>530</v>
       </c>
       <c r="U12" t="n">
         <v>31</v>
       </c>
       <c r="V12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="W12" t="n">
         <v>31</v>
@@ -2124,22 +2124,22 @@
         <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Z12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AA12" t="n">
         <v>0.763</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.483</v>
+        <v>0.5</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2151,60 +2151,60 @@
         <v>0.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.385</v>
+        <v>0.393</v>
       </c>
       <c r="AK12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>614:35</t>
+          <t>659:07</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>274.12</v>
+        <v>286.12</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.652</v>
+        <v>0.654</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.671</v>
+        <v>0.673</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.127</v>
+        <v>1.129</v>
       </c>
       <c r="AS12" t="n">
         <v>0.161</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.258</v>
+        <v>0.245</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.5</v>
+        <v>1.652</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.194</v>
+        <v>0.189</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.193</v>
+        <v>0.207</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="13">
@@ -2214,67 +2214,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
+        <v>91</v>
+      </c>
+      <c r="H13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I13" t="n">
         <v>84</v>
       </c>
-      <c r="H13" t="n">
-        <v>64</v>
-      </c>
-      <c r="I13" t="n">
-        <v>78</v>
-      </c>
       <c r="J13" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K13" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L13" t="n">
         <v>35</v>
       </c>
       <c r="M13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R13" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="S13" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="T13" t="n">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="U13" t="n">
         <v>32</v>
       </c>
       <c r="V13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="W13" t="n">
         <v>15</v>
@@ -2283,87 +2283,87 @@
         <v>9</v>
       </c>
       <c r="Y13" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="Z13" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.791</v>
+        <v>0.806</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
       </c>
       <c r="AF13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI13" t="n">
         <v>19</v>
       </c>
-      <c r="AG13" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>17</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>0.588</v>
+        <v>0.579</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.373</v>
+        <v>0.361</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>475:38</t>
+          <t>515:07</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>250.32</v>
+        <v>267.96</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.556</v>
+        <v>0.546</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.619</v>
+        <v>0.613</v>
       </c>
       <c r="AR13" t="n">
         <v>1.011</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.184</v>
+        <v>0.175</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.376</v>
+        <v>0.38</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.13</v>
+        <v>2.213</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.229</v>
+        <v>0.227</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.094</v>
+        <v>0.104</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="14">
@@ -2516,10 +2516,10 @@
         <v>0.199</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.227</v>
+        <v>0.226</v>
       </c>
       <c r="AY14" t="n">
         <v>0.011</v>
@@ -2532,28 +2532,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I15" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J15" t="n">
         <v>22</v>
@@ -2568,7 +2568,7 @@
         <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2580,19 +2580,19 @@
         <v>20</v>
       </c>
       <c r="R15" t="n">
+        <v>36</v>
+      </c>
+      <c r="S15" t="n">
         <v>32</v>
       </c>
-      <c r="S15" t="n">
-        <v>28</v>
-      </c>
       <c r="T15" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="U15" t="n">
+        <v>19</v>
+      </c>
+      <c r="V15" t="n">
         <v>18</v>
-      </c>
-      <c r="V15" t="n">
-        <v>17</v>
       </c>
       <c r="W15" t="n">
         <v>12</v>
@@ -2601,22 +2601,22 @@
         <v>7</v>
       </c>
       <c r="Y15" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="Z15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.614</v>
+        <v>0.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.357</v>
+        <v>0.344</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2628,45 +2628,45 @@
         <v>0.286</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="AK15" t="n">
         <v>8</v>
       </c>
       <c r="AL15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>339:51</t>
+          <t>375:21</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>132.96</v>
+        <v>146.48</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.553</v>
+        <v>0.534</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.922</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.15</v>
+        <v>0.137</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.153</v>
+        <v>0.185</v>
       </c>
       <c r="AU15" t="n">
         <v>1.1</v>
@@ -2675,13 +2675,13 @@
         <v>0.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.154</v>
+        <v>0.139</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -2691,153 +2691,153 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E16" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="H16" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I16" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J16" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K16" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L16" t="n">
         <v>14</v>
       </c>
       <c r="M16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S16" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="T16" t="n">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="V16" t="n">
         <v>39</v>
       </c>
       <c r="W16" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="X16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="Z16" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="AA16" t="n">
         <v>0.803</v>
       </c>
       <c r="AB16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.27</v>
+        <v>0.293</v>
       </c>
       <c r="AE16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF16" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="AG16" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>41</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>115</v>
+      </c>
+      <c r="AM16" t="n">
         <v>0.357</v>
       </c>
-      <c r="AH16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>39</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>106</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.368</v>
-      </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>497:16</t>
+          <t>535:46</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>315.24</v>
+        <v>344.88</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.602</v>
+        <v>0.596</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.079</v>
+        <v>1.067</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.247</v>
+        <v>0.244</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.788</v>
+        <v>2.75</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.276</v>
+        <v>0.281</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="AY16" t="n">
         <v>0.096</v>
@@ -2850,91 +2850,91 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H17" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J17" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M17" t="n">
         <v>17</v>
       </c>
       <c r="N17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R17" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="T17" t="n">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="U17" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="V17" t="n">
         <v>33</v>
       </c>
       <c r="W17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="Z17" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.722</v>
+        <v>0.742</v>
       </c>
       <c r="AB17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.404</v>
+        <v>0.408</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -2946,60 +2946,60 @@
         <v>0.286</v>
       </c>
       <c r="AH17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.263</v>
+        <v>0.261</v>
       </c>
       <c r="AK17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.451</v>
+        <v>0.455</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>559:30</t>
+          <t>600:29</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>248</v>
+        <v>269.2</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.6</v>
+        <v>0.612</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.02</v>
+        <v>1.051</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.149</v>
+        <v>0.141</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.206</v>
+        <v>0.213</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.135</v>
+        <v>2.211</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.096</v>
+        <v>0.092</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18">
@@ -3009,40 +3009,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D18" t="n">
+        <v>62</v>
+      </c>
+      <c r="E18" t="n">
+        <v>92</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="n">
+        <v>48</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21</v>
+      </c>
+      <c r="K18" t="n">
         <v>53</v>
       </c>
-      <c r="E18" t="n">
-        <v>83</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>19</v>
-      </c>
-      <c r="I18" t="n">
-        <v>46</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" t="n">
-        <v>48</v>
-      </c>
       <c r="L18" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N18" t="n">
         <v>18</v>
@@ -3057,43 +3057,43 @@
         <v>16</v>
       </c>
       <c r="R18" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="S18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T18" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="U18" t="n">
         <v>14</v>
       </c>
       <c r="V18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="Z18" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.606</v>
+        <v>0.633</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.44</v>
+        <v>0.462</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3124,41 +3124,41 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>372:28</t>
+          <t>409:49</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>119.24</v>
+        <v>129.12</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.639</v>
+        <v>0.674</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.605</v>
+        <v>0.636</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.048</v>
+        <v>1.115</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.134</v>
+        <v>0.124</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.229</v>
+        <v>0.217</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.25</v>
+        <v>1.312</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="AX18" t="n">
         <v>0.138</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="19">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" t="n">
         <v>206</v>
@@ -3317,7 +3317,7 @@
         <v>0.059</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.08</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="20">
@@ -3467,7 +3467,7 @@
         <v>2</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.662</v>
+        <v>0.664</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
@@ -3486,40 +3486,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3534,49 +3534,49 @@
         <v>3</v>
       </c>
       <c r="R21" t="n">
+        <v>9</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z21" t="n">
         <v>4</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-7</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3591,51 +3591,51 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>39:16</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>3</v>
+        <v>15.76</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.079</v>
       </c>
       <c r="AS21" t="n">
-        <v>1</v>
+        <v>0.19</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.196</v>
+        <v>0.175</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="22">
@@ -3645,67 +3645,67 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C22" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D22" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>68</v>
+      </c>
+      <c r="F22" t="n">
         <v>41</v>
       </c>
-      <c r="E22" t="n">
-        <v>62</v>
-      </c>
-      <c r="F22" t="n">
-        <v>40</v>
-      </c>
       <c r="G22" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J22" t="n">
         <v>29</v>
       </c>
       <c r="K22" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L22" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M22" t="n">
         <v>24</v>
       </c>
       <c r="N22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R22" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="S22" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="T22" t="n">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="U22" t="n">
         <v>25</v>
       </c>
       <c r="V22" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="W22" t="n">
         <v>24</v>
@@ -3714,87 +3714,87 @@
         <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Z22" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.649</v>
+        <v>0.667</v>
       </c>
       <c r="AB22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.444</v>
+        <v>0.45</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.52</v>
+        <v>0.519</v>
       </c>
       <c r="AK22" t="n">
         <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>494:46</t>
+          <t>524:08</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>198.72</v>
+        <v>209.16</v>
       </c>
       <c r="AP22" t="n">
         <v>0.605</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.599</v>
+        <v>0.601</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.107</v>
+        <v>1.109</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="AT22" t="n">
         <v>0.108</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.933</v>
+        <v>1.812</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.092</v>
+        <v>0.093</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.164</v>
+        <v>0.163</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="23">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L23" t="n">
         <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -3852,13 +3852,13 @@
         <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="U23" t="n">
         <v>6</v>
@@ -3873,13 +3873,13 @@
         <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.6</v>
+        <v>0.583</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH23" t="n">
         <v>1</v>
@@ -3912,45 +3912,45 @@
         <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM23" t="n">
         <v>0</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>143:01</t>
+          <t>152:04</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>26.76</v>
+        <v>29.64</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.237</v>
+        <v>0.262</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.289</v>
+        <v>0.317</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.448</v>
+        <v>0.506</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.224</v>
+        <v>0.202</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.158</v>
+        <v>0.19</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.333</v>
+        <v>2.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.081</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.15</v>
+        <v>0.147</v>
       </c>
       <c r="AY23" t="n">
         <v>0.013</v>
@@ -3963,22 +3963,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H24" t="n">
         <v>15</v>
@@ -3990,10 +3990,10 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
+        <v>21</v>
+      </c>
+      <c r="L24" t="n">
         <v>19</v>
-      </c>
-      <c r="L24" t="n">
-        <v>18</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
@@ -4005,25 +4005,25 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T24" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W24" t="n">
         <v>3</v>
@@ -4032,13 +4032,13 @@
         <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Z24" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.607</v>
+        <v>0.627</v>
       </c>
       <c r="AB24" t="n">
         <v>1</v>
@@ -4068,51 +4068,51 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.182</v>
+        <v>0.231</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>173:38</t>
+          <t>186:57</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>68.31999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.511</v>
+        <v>0.55</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.532</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.893</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AS24" t="n">
         <v>0.161</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="25">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -4149,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -4281,153 +4281,153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>3011</v>
+        <v>3218</v>
       </c>
       <c r="D26" t="n">
-        <v>696</v>
+        <v>752</v>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1288</v>
       </c>
       <c r="F26" t="n">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="G26" t="n">
-        <v>1043</v>
+        <v>1102</v>
       </c>
       <c r="H26" t="n">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="I26" t="n">
-        <v>692</v>
+        <v>728</v>
       </c>
       <c r="J26" t="n">
-        <v>664</v>
+        <v>701</v>
       </c>
       <c r="K26" t="n">
-        <v>839</v>
+        <v>895</v>
       </c>
       <c r="L26" t="n">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="M26" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="N26" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
+        <v>408</v>
+      </c>
+      <c r="Q26" t="n">
         <v>393</v>
       </c>
-      <c r="Q26" t="n">
-        <v>378</v>
-      </c>
       <c r="R26" t="n">
-        <v>620</v>
+        <v>653</v>
       </c>
       <c r="S26" t="n">
-        <v>707</v>
+        <v>745</v>
       </c>
       <c r="T26" t="n">
-        <v>3747</v>
+        <v>4011</v>
       </c>
       <c r="U26" t="n">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="V26" t="n">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="W26" t="n">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="X26" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y26" t="n">
-        <v>974</v>
+        <v>1038</v>
       </c>
       <c r="Z26" t="n">
-        <v>1335</v>
+        <v>1415</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.73</v>
+        <v>0.734</v>
       </c>
       <c r="AB26" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="AC26" t="n">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.399</v>
+        <v>0.403</v>
       </c>
       <c r="AE26" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="AH26" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AI26" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AJ26" t="n">
         <v>0.397</v>
       </c>
       <c r="AK26" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="AL26" t="n">
-        <v>796</v>
+        <v>840</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6800:00</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2942.48</v>
+        <v>3118.32</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.591</v>
+        <v>0.594</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.023</v>
+        <v>1.032</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.22</v>
+        <v>0.218</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.69</v>
+        <v>1.718</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4440,153 +4440,153 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2671</v>
+        <v>2829</v>
       </c>
       <c r="D27" t="n">
-        <v>640</v>
+        <v>683</v>
       </c>
       <c r="E27" t="n">
-        <v>1194</v>
+        <v>1273</v>
       </c>
       <c r="F27" t="n">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="G27" t="n">
-        <v>964</v>
+        <v>1018</v>
       </c>
       <c r="H27" t="n">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="I27" t="n">
-        <v>584</v>
+        <v>612</v>
       </c>
       <c r="J27" t="n">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="K27" t="n">
-        <v>760</v>
+        <v>807</v>
       </c>
       <c r="L27" t="n">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="M27" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N27" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="Q27" t="n">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="R27" t="n">
-        <v>707</v>
+        <v>745</v>
       </c>
       <c r="S27" t="n">
-        <v>617</v>
+        <v>650</v>
       </c>
       <c r="T27" t="n">
-        <v>2870</v>
+        <v>3024</v>
       </c>
       <c r="U27" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="V27" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="W27" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="X27" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="Y27" t="n">
-        <v>857</v>
+        <v>901</v>
       </c>
       <c r="Z27" t="n">
-        <v>1177</v>
+        <v>1233</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="AB27" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="AC27" t="n">
-        <v>388</v>
+        <v>421</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.415</v>
+        <v>0.418</v>
       </c>
       <c r="AE27" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AF27" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.319</v>
+        <v>0.316</v>
       </c>
       <c r="AH27" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AI27" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.37</v>
+        <v>0.364</v>
       </c>
       <c r="AK27" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="AL27" t="n">
-        <v>699</v>
+        <v>738</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.31</v>
+        <v>0.312</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6800:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2851.96</v>
+        <v>3024.28</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.516</v>
+        <v>0.515</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.553</v>
+        <v>0.552</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AS27" t="n">
         <v>0.153</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.227</v>
+        <v>1.194</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4656,144 +4656,144 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>9.567</v>
+        <v>9.781000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>1.567</v>
+        <v>1.688</v>
       </c>
       <c r="E29" t="n">
-        <v>2.933</v>
+        <v>3.125</v>
       </c>
       <c r="F29" t="n">
-        <v>1.667</v>
+        <v>1.688</v>
       </c>
       <c r="G29" t="n">
-        <v>5.133</v>
+        <v>5.094</v>
       </c>
       <c r="H29" t="n">
-        <v>1.433</v>
+        <v>1.344</v>
       </c>
       <c r="I29" t="n">
-        <v>1.767</v>
+        <v>1.719</v>
       </c>
       <c r="J29" t="n">
-        <v>1.9</v>
+        <v>1.844</v>
       </c>
       <c r="K29" t="n">
-        <v>1.6</v>
+        <v>1.594</v>
       </c>
       <c r="L29" t="n">
-        <v>0.533</v>
+        <v>0.531</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.267</v>
+        <v>1.219</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.267</v>
+        <v>1.219</v>
       </c>
       <c r="R29" t="n">
-        <v>1.833</v>
+        <v>1.75</v>
       </c>
       <c r="S29" t="n">
-        <v>1.933</v>
+        <v>1.906</v>
       </c>
       <c r="T29" t="n">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="U29" t="n">
-        <v>1.7</v>
+        <v>1.688</v>
       </c>
       <c r="V29" t="n">
-        <v>1.167</v>
+        <v>1.219</v>
       </c>
       <c r="W29" t="n">
-        <v>1.367</v>
+        <v>1.375</v>
       </c>
       <c r="X29" t="n">
-        <v>0.733</v>
+        <v>0.719</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.3</v>
+        <v>2.281</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.1</v>
+        <v>3.125</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.742</v>
+        <v>0.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.633</v>
+        <v>0.656</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.579</v>
+        <v>0.571</v>
       </c>
       <c r="AE29" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>0.333</v>
       </c>
-      <c r="AF29" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.343</v>
-      </c>
       <c r="AK29" t="n">
-        <v>1.267</v>
+        <v>1.312</v>
       </c>
       <c r="AL29" t="n">
-        <v>3.967</v>
+        <v>3.969</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.319</v>
+        <v>0.331</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>10.111</v>
+        <v>10.194</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.504</v>
+        <v>0.513</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.541</v>
+        <v>0.545</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.946</v>
+        <v>0.96</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.178</v>
+        <v>0.163</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.5</v>
+        <v>1.513</v>
       </c>
       <c r="AV29" t="n">
         <v>0.238</v>
@@ -4802,10 +4802,10 @@
         <v>0.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="30">
@@ -4815,156 +4815,156 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C30" t="n">
-        <v>11.261</v>
+        <v>11.2</v>
       </c>
       <c r="D30" t="n">
-        <v>3.261</v>
+        <v>3.24</v>
       </c>
       <c r="E30" t="n">
-        <v>5.522</v>
+        <v>5.36</v>
       </c>
       <c r="F30" t="n">
-        <v>1.261</v>
+        <v>1.28</v>
       </c>
       <c r="G30" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="H30" t="n">
-        <v>0.957</v>
+        <v>0.88</v>
       </c>
       <c r="I30" t="n">
-        <v>1.304</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
-        <v>2.391</v>
+        <v>2.32</v>
       </c>
       <c r="K30" t="n">
-        <v>3.304</v>
+        <v>3.16</v>
       </c>
       <c r="L30" t="n">
-        <v>0.826</v>
+        <v>0.76</v>
       </c>
       <c r="M30" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="N30" t="n">
-        <v>0.739</v>
+        <v>0.68</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.522</v>
+        <v>1.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.522</v>
+        <v>1.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.826</v>
+        <v>1.84</v>
       </c>
       <c r="S30" t="n">
-        <v>1.826</v>
+        <v>1.72</v>
       </c>
       <c r="T30" t="n">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="U30" t="n">
-        <v>2.087</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>0.522</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W30" t="n">
-        <v>1.348</v>
+        <v>1.32</v>
       </c>
       <c r="X30" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.609</v>
+        <v>2.56</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.609</v>
+        <v>3.48</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.723</v>
+        <v>0.736</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.957</v>
+        <v>0.88</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.913</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.652</v>
+        <v>0.68</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.304</v>
+        <v>1.28</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.391</v>
+        <v>0.36</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.913</v>
+        <v>0.84</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.429</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.217</v>
+        <v>2.24</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.392</v>
+        <v>0.411</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>10.748</v>
+        <v>10.568</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.595</v>
+        <v>0.611</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.61</v>
+        <v>0.624</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.048</v>
+        <v>1.06</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.142</v>
+        <v>0.151</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.111</v>
+        <v>0.104</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.571</v>
+        <v>1.45</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.041</v>
+        <v>0.038</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.166</v>
+        <v>0.16</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.083</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="31">
@@ -5114,7 +5114,7 @@
         <v>1.143</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="AW31" t="n">
         <v>0.068</v>
@@ -5123,7 +5123,7 @@
         <v>0.115</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="32">
@@ -5276,13 +5276,13 @@
         <v>0.203</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AX32" t="n">
         <v>0.122</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>10.655</v>
+        <v>10.419</v>
       </c>
       <c r="D33" t="n">
-        <v>3.31</v>
+        <v>3.226</v>
       </c>
       <c r="E33" t="n">
-        <v>4.655</v>
+        <v>4.516</v>
       </c>
       <c r="F33" t="n">
-        <v>0.759</v>
+        <v>0.774</v>
       </c>
       <c r="G33" t="n">
-        <v>2.172</v>
+        <v>2.194</v>
       </c>
       <c r="H33" t="n">
-        <v>1.759</v>
+        <v>1.645</v>
       </c>
       <c r="I33" t="n">
-        <v>2.517</v>
+        <v>2.355</v>
       </c>
       <c r="J33" t="n">
-        <v>2.276</v>
+        <v>2.452</v>
       </c>
       <c r="K33" t="n">
-        <v>3.828</v>
+        <v>4.129</v>
       </c>
       <c r="L33" t="n">
-        <v>1.862</v>
+        <v>1.871</v>
       </c>
       <c r="M33" t="n">
-        <v>0.793</v>
+        <v>0.839</v>
       </c>
       <c r="N33" t="n">
-        <v>0.448</v>
+        <v>0.452</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.517</v>
+        <v>1.484</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.517</v>
+        <v>1.484</v>
       </c>
       <c r="R33" t="n">
-        <v>1.241</v>
+        <v>1.194</v>
       </c>
       <c r="S33" t="n">
-        <v>3.069</v>
+        <v>3.032</v>
       </c>
       <c r="T33" t="n">
-        <v>483</v>
+        <v>530</v>
       </c>
       <c r="U33" t="n">
-        <v>1.069</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>1.897</v>
+        <v>1.839</v>
       </c>
       <c r="W33" t="n">
-        <v>1.069</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>0.724</v>
+        <v>0.677</v>
       </c>
       <c r="Y33" t="n">
-        <v>4.448</v>
+        <v>4.258</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.828</v>
+        <v>5.581</v>
       </c>
       <c r="AA33" t="n">
         <v>0.763</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0.968</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.483</v>
+        <v>0.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.138</v>
+        <v>0.129</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.345</v>
+        <v>0.323</v>
       </c>
       <c r="AG33" t="n">
         <v>0.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.345</v>
+        <v>0.355</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.897</v>
+        <v>0.903</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.385</v>
+        <v>0.393</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.414</v>
+        <v>0.419</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.276</v>
+        <v>1.29</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>9.452</v>
+        <v>9.23</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.652</v>
+        <v>0.654</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.671</v>
+        <v>0.673</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.127</v>
+        <v>1.129</v>
       </c>
       <c r="AS33" t="n">
         <v>0.161</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.258</v>
+        <v>0.245</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.5</v>
+        <v>1.652</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.194</v>
+        <v>0.189</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.193</v>
+        <v>0.207</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.077</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="34">
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C34" t="n">
-        <v>9.369999999999999</v>
+        <v>9.345000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>1.556</v>
+        <v>1.552</v>
       </c>
       <c r="E34" t="n">
-        <v>3.185</v>
+        <v>3.207</v>
       </c>
       <c r="F34" t="n">
-        <v>1.296</v>
+        <v>1.276</v>
       </c>
       <c r="G34" t="n">
-        <v>3.111</v>
+        <v>3.138</v>
       </c>
       <c r="H34" t="n">
-        <v>2.37</v>
+        <v>2.414</v>
       </c>
       <c r="I34" t="n">
-        <v>2.889</v>
+        <v>2.897</v>
       </c>
       <c r="J34" t="n">
-        <v>3.63</v>
+        <v>3.586</v>
       </c>
       <c r="K34" t="n">
-        <v>1.556</v>
+        <v>1.724</v>
       </c>
       <c r="L34" t="n">
-        <v>1.296</v>
+        <v>1.207</v>
       </c>
       <c r="M34" t="n">
-        <v>0.481</v>
+        <v>0.517</v>
       </c>
       <c r="N34" t="n">
-        <v>0.519</v>
+        <v>0.517</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.704</v>
+        <v>1.621</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.704</v>
+        <v>1.621</v>
       </c>
       <c r="R34" t="n">
-        <v>1.519</v>
+        <v>1.517</v>
       </c>
       <c r="S34" t="n">
-        <v>3.222</v>
+        <v>3.207</v>
       </c>
       <c r="T34" t="n">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="U34" t="n">
-        <v>1.185</v>
+        <v>1.103</v>
       </c>
       <c r="V34" t="n">
-        <v>1.296</v>
+        <v>1.345</v>
       </c>
       <c r="W34" t="n">
-        <v>0.556</v>
+        <v>0.517</v>
       </c>
       <c r="X34" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.37</v>
+        <v>3.448</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.259</v>
+        <v>4.276</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.791</v>
+        <v>0.806</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.407</v>
+        <v>0.379</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.111</v>
+        <v>1.069</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.704</v>
+        <v>0.759</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.211</v>
+        <v>0.182</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.37</v>
+        <v>0.379</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.63</v>
+        <v>0.655</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.588</v>
+        <v>0.579</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.926</v>
+        <v>0.897</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.481</v>
+        <v>2.483</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.373</v>
+        <v>0.361</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>9.271000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.556</v>
+        <v>0.546</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.619</v>
+        <v>0.613</v>
       </c>
       <c r="AR34" t="n">
         <v>1.011</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.184</v>
+        <v>0.175</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.376</v>
+        <v>0.38</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.13</v>
+        <v>2.213</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.229</v>
+        <v>0.227</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.078</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.094</v>
+        <v>0.104</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.119</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="35">
@@ -5753,13 +5753,13 @@
         <v>0.199</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.227</v>
+        <v>0.226</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="36">
@@ -5769,141 +5769,141 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C36" t="n">
-        <v>5.682</v>
+        <v>5.625</v>
       </c>
       <c r="D36" t="n">
-        <v>1.818</v>
+        <v>1.708</v>
       </c>
       <c r="E36" t="n">
-        <v>3.227</v>
+        <v>3.208</v>
       </c>
       <c r="F36" t="n">
-        <v>0.455</v>
+        <v>0.458</v>
       </c>
       <c r="G36" t="n">
-        <v>1.227</v>
+        <v>1.292</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="I36" t="n">
-        <v>1.545</v>
+        <v>1.75</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0.917</v>
       </c>
       <c r="K36" t="n">
-        <v>2.227</v>
+        <v>2.042</v>
       </c>
       <c r="L36" t="n">
-        <v>0.773</v>
+        <v>0.708</v>
       </c>
       <c r="M36" t="n">
-        <v>0.864</v>
+        <v>0.792</v>
       </c>
       <c r="N36" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="T36" t="n">
+        <v>153</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W36" t="n">
         <v>0.5</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.455</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.273</v>
-      </c>
-      <c r="T36" t="n">
-        <v>152</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.545</v>
-      </c>
       <c r="X36" t="n">
-        <v>0.318</v>
+        <v>0.292</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.955</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.182</v>
+        <v>3.333</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.614</v>
+        <v>0.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.455</v>
+        <v>0.458</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.273</v>
+        <v>1.333</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.357</v>
+        <v>0.344</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.091</v>
+        <v>0.083</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.318</v>
+        <v>0.292</v>
       </c>
       <c r="AG36" t="n">
         <v>0.286</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.091</v>
+        <v>0.125</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.591</v>
+        <v>0.625</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.636</v>
+        <v>0.667</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>6.044</v>
+        <v>6.103</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.553</v>
+        <v>0.534</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.922</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.15</v>
+        <v>0.137</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.153</v>
+        <v>0.185</v>
       </c>
       <c r="AU36" t="n">
         <v>1.1</v>
@@ -5912,13 +5912,13 @@
         <v>0.17</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.154</v>
+        <v>0.139</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="37">
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C37" t="n">
-        <v>14.167</v>
+        <v>14.154</v>
       </c>
       <c r="D37" t="n">
-        <v>2.667</v>
+        <v>2.731</v>
       </c>
       <c r="E37" t="n">
-        <v>5.25</v>
+        <v>5.346</v>
       </c>
       <c r="F37" t="n">
-        <v>2.083</v>
+        <v>2.038</v>
       </c>
       <c r="G37" t="n">
-        <v>5.208</v>
+        <v>5.231</v>
       </c>
       <c r="H37" t="n">
-        <v>2.583</v>
+        <v>2.577</v>
       </c>
       <c r="I37" t="n">
-        <v>2.958</v>
+        <v>2.962</v>
       </c>
       <c r="J37" t="n">
-        <v>3.833</v>
+        <v>3.808</v>
       </c>
       <c r="K37" t="n">
-        <v>2.042</v>
+        <v>2.038</v>
       </c>
       <c r="L37" t="n">
-        <v>0.583</v>
+        <v>0.538</v>
       </c>
       <c r="M37" t="n">
-        <v>1.208</v>
+        <v>1.154</v>
       </c>
       <c r="N37" t="n">
-        <v>0.333</v>
+        <v>0.423</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.375</v>
+        <v>1.385</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.375</v>
+        <v>1.385</v>
       </c>
       <c r="R37" t="n">
-        <v>1.125</v>
+        <v>1.077</v>
       </c>
       <c r="S37" t="n">
-        <v>3.25</v>
+        <v>3.192</v>
       </c>
       <c r="T37" t="n">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="U37" t="n">
-        <v>2.542</v>
+        <v>2.846</v>
       </c>
       <c r="V37" t="n">
-        <v>1.625</v>
+        <v>1.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0.833</v>
+        <v>0.923</v>
       </c>
       <c r="X37" t="n">
-        <v>0.5</v>
+        <v>0.577</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.417</v>
+        <v>4.385</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.5</v>
+        <v>5.462</v>
       </c>
       <c r="AA37" t="n">
         <v>0.803</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.417</v>
+        <v>0.462</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.542</v>
+        <v>1.577</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.27</v>
+        <v>0.293</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.417</v>
+        <v>0.462</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.167</v>
+        <v>1.269</v>
       </c>
       <c r="AG37" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.577</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>4.423</v>
+      </c>
+      <c r="AM37" t="n">
         <v>0.357</v>
       </c>
-      <c r="AH37" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>4.417</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.368</v>
-      </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>13.135</v>
+        <v>13.265</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.602</v>
+        <v>0.596</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.079</v>
+        <v>1.067</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.247</v>
+        <v>0.244</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.788</v>
+        <v>2.75</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.276</v>
+        <v>0.281</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="38">
@@ -6087,156 +6087,156 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C38" t="n">
-        <v>8.724</v>
+        <v>9.129</v>
       </c>
       <c r="D38" t="n">
-        <v>2.241</v>
+        <v>2.355</v>
       </c>
       <c r="E38" t="n">
-        <v>4.103</v>
+        <v>4.161</v>
       </c>
       <c r="F38" t="n">
-        <v>0.966</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>2.414</v>
+        <v>2.516</v>
       </c>
       <c r="H38" t="n">
-        <v>1.345</v>
+        <v>1.419</v>
       </c>
       <c r="I38" t="n">
-        <v>1.724</v>
+        <v>1.774</v>
       </c>
       <c r="J38" t="n">
-        <v>2.724</v>
+        <v>2.71</v>
       </c>
       <c r="K38" t="n">
-        <v>1.724</v>
+        <v>1.677</v>
       </c>
       <c r="L38" t="n">
-        <v>0.793</v>
+        <v>0.806</v>
       </c>
       <c r="M38" t="n">
-        <v>0.586</v>
+        <v>0.548</v>
       </c>
       <c r="N38" t="n">
-        <v>0.759</v>
+        <v>0.774</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.276</v>
+        <v>1.226</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.276</v>
+        <v>1.226</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.323</v>
       </c>
       <c r="S38" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="T38" t="n">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="U38" t="n">
-        <v>1.138</v>
+        <v>1.387</v>
       </c>
       <c r="V38" t="n">
-        <v>1.138</v>
+        <v>1.065</v>
       </c>
       <c r="W38" t="n">
-        <v>1.069</v>
+        <v>1.065</v>
       </c>
       <c r="X38" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.862</v>
+        <v>3.065</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.966</v>
+        <v>4.129</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.722</v>
+        <v>0.742</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.655</v>
+        <v>0.645</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.621</v>
+        <v>1.581</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.404</v>
+        <v>0.408</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.241</v>
+        <v>0.226</v>
       </c>
       <c r="AG38" t="n">
         <v>0.286</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.172</v>
+        <v>0.194</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.655</v>
+        <v>0.742</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.263</v>
+        <v>0.261</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.793</v>
+        <v>0.806</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.759</v>
+        <v>1.774</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.451</v>
+        <v>0.455</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>8.552</v>
+        <v>8.683999999999999</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.577</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.6</v>
+        <v>0.612</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.02</v>
+        <v>1.051</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.149</v>
+        <v>0.141</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.206</v>
+        <v>0.213</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.135</v>
+        <v>2.211</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.096</v>
+        <v>0.092</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="39">
@@ -6246,16 +6246,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>5.333</v>
       </c>
       <c r="D39" t="n">
-        <v>2.12</v>
+        <v>2.296</v>
       </c>
       <c r="E39" t="n">
-        <v>3.32</v>
+        <v>3.407</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6264,79 +6264,79 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.76</v>
+        <v>0.741</v>
       </c>
       <c r="I39" t="n">
-        <v>1.84</v>
+        <v>1.778</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8</v>
+        <v>0.778</v>
       </c>
       <c r="K39" t="n">
-        <v>1.92</v>
+        <v>1.963</v>
       </c>
       <c r="L39" t="n">
-        <v>1.76</v>
+        <v>1.852</v>
       </c>
       <c r="M39" t="n">
-        <v>0.48</v>
+        <v>0.481</v>
       </c>
       <c r="N39" t="n">
-        <v>0.72</v>
+        <v>0.667</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.64</v>
+        <v>0.593</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.64</v>
+        <v>0.593</v>
       </c>
       <c r="R39" t="n">
-        <v>1.92</v>
+        <v>1.926</v>
       </c>
       <c r="S39" t="n">
-        <v>1.68</v>
+        <v>1.593</v>
       </c>
       <c r="T39" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="U39" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.519</v>
       </c>
       <c r="V39" t="n">
-        <v>0.88</v>
+        <v>0.852</v>
       </c>
       <c r="W39" t="n">
-        <v>0.08</v>
+        <v>0.222</v>
       </c>
       <c r="X39" t="n">
-        <v>0.04</v>
+        <v>0.111</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.4</v>
+        <v>2.556</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.96</v>
+        <v>4.037</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.606</v>
+        <v>0.633</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.44</v>
+        <v>0.444</v>
       </c>
       <c r="AC39" t="n">
-        <v>1</v>
+        <v>0.963</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.44</v>
+        <v>0.462</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.2</v>
+        <v>0.185</v>
       </c>
       <c r="AG39" t="n">
         <v>0.2</v>
@@ -6361,41 +6361,41 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>4.77</v>
+        <v>4.782</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.639</v>
+        <v>0.674</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.605</v>
+        <v>0.636</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.048</v>
+        <v>1.115</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.134</v>
+        <v>0.124</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.229</v>
+        <v>0.217</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.25</v>
+        <v>1.312</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="AX39" t="n">
         <v>0.138</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="40">
@@ -6405,126 +6405,126 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C40" t="n">
-        <v>7.357</v>
+        <v>7.103</v>
       </c>
       <c r="D40" t="n">
-        <v>1.393</v>
+        <v>1.345</v>
       </c>
       <c r="E40" t="n">
-        <v>2.464</v>
+        <v>2.379</v>
       </c>
       <c r="F40" t="n">
-        <v>1.071</v>
+        <v>1.034</v>
       </c>
       <c r="G40" t="n">
-        <v>3.286</v>
+        <v>3.172</v>
       </c>
       <c r="H40" t="n">
-        <v>1.357</v>
+        <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>1.643</v>
+        <v>1.586</v>
       </c>
       <c r="J40" t="n">
-        <v>2.857</v>
+        <v>2.759</v>
       </c>
       <c r="K40" t="n">
-        <v>0.964</v>
+        <v>0.931</v>
       </c>
       <c r="L40" t="n">
-        <v>0.857</v>
+        <v>0.828</v>
       </c>
       <c r="M40" t="n">
-        <v>0.714</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>0.321</v>
+        <v>0.31</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.893</v>
+        <v>0.862</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.893</v>
+        <v>0.862</v>
       </c>
       <c r="R40" t="n">
-        <v>1.821</v>
+        <v>1.759</v>
       </c>
       <c r="S40" t="n">
-        <v>1.393</v>
+        <v>1.345</v>
       </c>
       <c r="T40" t="n">
         <v>229</v>
       </c>
       <c r="U40" t="n">
-        <v>1.393</v>
+        <v>1.345</v>
       </c>
       <c r="V40" t="n">
-        <v>0.821</v>
+        <v>0.793</v>
       </c>
       <c r="W40" t="n">
-        <v>0.857</v>
+        <v>0.828</v>
       </c>
       <c r="X40" t="n">
-        <v>0.5</v>
+        <v>0.483</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.25</v>
+        <v>2.172</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.714</v>
+        <v>2.621</v>
       </c>
       <c r="AA40" t="n">
         <v>0.829</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.286</v>
+        <v>0.276</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.893</v>
+        <v>0.862</v>
       </c>
       <c r="AD40" t="n">
         <v>0.32</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.214</v>
+        <v>0.207</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.5</v>
+        <v>0.483</v>
       </c>
       <c r="AG40" t="n">
         <v>0.429</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.179</v>
+        <v>0.172</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.321</v>
+        <v>0.31</v>
       </c>
       <c r="AJ40" t="n">
         <v>0.556</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.893</v>
+        <v>0.862</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.964</v>
+        <v>2.862</v>
       </c>
       <c r="AM40" t="n">
         <v>0.301</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>7.366</v>
+        <v>7.112</v>
       </c>
       <c r="AP40" t="n">
         <v>0.522</v>
@@ -6554,7 +6554,7 @@
         <v>0.059</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.092</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -6704,7 +6704,7 @@
         <v>2</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.662</v>
+        <v>0.664</v>
       </c>
       <c r="AW41" t="n">
         <v>0</v>
@@ -6723,40 +6723,40 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -6765,25 +6765,25 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" t="n">
-        <v>3</v>
-      </c>
-      <c r="R42" t="n">
-        <v>4</v>
-      </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>-7</v>
+        <v>8</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -6792,28 +6792,28 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -6828,51 +6828,51 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>3</v>
+        <v>5.253</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.079</v>
       </c>
       <c r="AS42" t="n">
-        <v>1</v>
+        <v>0.19</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.196</v>
+        <v>0.175</v>
       </c>
       <c r="AW42" t="n">
         <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="43">
@@ -6882,156 +6882,156 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C43" t="n">
-        <v>7.586</v>
+        <v>7.484</v>
       </c>
       <c r="D43" t="n">
-        <v>1.414</v>
+        <v>1.452</v>
       </c>
       <c r="E43" t="n">
-        <v>2.138</v>
+        <v>2.194</v>
       </c>
       <c r="F43" t="n">
-        <v>1.379</v>
+        <v>1.323</v>
       </c>
       <c r="G43" t="n">
-        <v>3.621</v>
+        <v>3.484</v>
       </c>
       <c r="H43" t="n">
-        <v>0.621</v>
+        <v>0.613</v>
       </c>
       <c r="I43" t="n">
-        <v>1.31</v>
+        <v>1.258</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>2.621</v>
+        <v>2.581</v>
       </c>
       <c r="L43" t="n">
-        <v>1.483</v>
+        <v>1.484</v>
       </c>
       <c r="M43" t="n">
-        <v>0.828</v>
+        <v>0.774</v>
       </c>
       <c r="N43" t="n">
-        <v>0.897</v>
+        <v>0.871</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.517</v>
+        <v>0.516</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.517</v>
+        <v>0.516</v>
       </c>
       <c r="R43" t="n">
-        <v>1.759</v>
+        <v>1.806</v>
       </c>
       <c r="S43" t="n">
-        <v>1.345</v>
+        <v>1.387</v>
       </c>
       <c r="T43" t="n">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="U43" t="n">
-        <v>0.862</v>
+        <v>0.806</v>
       </c>
       <c r="V43" t="n">
-        <v>0.759</v>
+        <v>0.871</v>
       </c>
       <c r="W43" t="n">
-        <v>0.828</v>
+        <v>0.774</v>
       </c>
       <c r="X43" t="n">
-        <v>0.379</v>
+        <v>0.355</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.724</v>
+        <v>1.742</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.655</v>
+        <v>2.613</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.649</v>
+        <v>0.667</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.276</v>
+        <v>0.29</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.621</v>
+        <v>0.645</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.444</v>
+        <v>0.45</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.172</v>
+        <v>0.194</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.448</v>
+        <v>0.452</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.862</v>
+        <v>0.871</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.52</v>
+        <v>0.519</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.931</v>
+        <v>0.871</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.759</v>
+        <v>2.613</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.337</v>
+        <v>0.333</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>6.852</v>
+        <v>6.747</v>
       </c>
       <c r="AP43" t="n">
         <v>0.605</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.599</v>
+        <v>0.601</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.107</v>
+        <v>1.109</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="AT43" t="n">
         <v>0.108</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.933</v>
+        <v>1.812</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.092</v>
+        <v>0.093</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.164</v>
+        <v>0.163</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="44">
@@ -7041,106 +7041,106 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C44" t="n">
-        <v>0.571</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.143</v>
+        <v>0.182</v>
       </c>
       <c r="E44" t="n">
-        <v>0.571</v>
+        <v>0.591</v>
       </c>
       <c r="F44" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="G44" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="T44" t="n">
+        <v>27</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="AG44" t="n">
         <v>0.333</v>
       </c>
-      <c r="H44" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.952</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="T44" t="n">
-        <v>21</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
       <c r="AH44" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.19</v>
+        <v>0.182</v>
       </c>
       <c r="AJ44" t="n">
         <v>0.25</v>
@@ -7149,45 +7149,45 @@
         <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.143</v>
+        <v>0.182</v>
       </c>
       <c r="AM44" t="n">
         <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>06:48</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>1.274</v>
+        <v>1.347</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.237</v>
+        <v>0.262</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.289</v>
+        <v>0.317</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.448</v>
+        <v>0.506</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.224</v>
+        <v>0.202</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.158</v>
+        <v>0.19</v>
       </c>
       <c r="AU44" t="n">
-        <v>2.333</v>
+        <v>2.5</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.081</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.15</v>
+        <v>0.147</v>
       </c>
       <c r="AY44" t="n">
         <v>0.02</v>
@@ -7200,88 +7200,88 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C45" t="n">
-        <v>2.905</v>
+        <v>3.043</v>
       </c>
       <c r="D45" t="n">
-        <v>0.952</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1.619</v>
+        <v>1.609</v>
       </c>
       <c r="F45" t="n">
-        <v>0.095</v>
+        <v>0.13</v>
       </c>
       <c r="G45" t="n">
-        <v>0.524</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.714</v>
+        <v>0.652</v>
       </c>
       <c r="I45" t="n">
-        <v>1.333</v>
+        <v>1.217</v>
       </c>
       <c r="J45" t="n">
-        <v>0.238</v>
+        <v>0.217</v>
       </c>
       <c r="K45" t="n">
-        <v>0.905</v>
+        <v>0.913</v>
       </c>
       <c r="L45" t="n">
-        <v>0.857</v>
+        <v>0.826</v>
       </c>
       <c r="M45" t="n">
-        <v>0.143</v>
+        <v>0.13</v>
       </c>
       <c r="N45" t="n">
-        <v>0.476</v>
+        <v>0.435</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.524</v>
+        <v>0.522</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.524</v>
+        <v>0.522</v>
       </c>
       <c r="R45" t="n">
-        <v>1.286</v>
+        <v>1.217</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
       <c r="T45" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U45" t="n">
-        <v>0.381</v>
+        <v>0.435</v>
       </c>
       <c r="V45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="W45" t="n">
-        <v>0.143</v>
+        <v>0.13</v>
       </c>
       <c r="X45" t="n">
-        <v>0.095</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.619</v>
+        <v>1.609</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.667</v>
+        <v>2.565</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.607</v>
+        <v>0.627</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.048</v>
+        <v>0.043</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.19</v>
+        <v>0.174</v>
       </c>
       <c r="AD45" t="n">
         <v>0.25</v>
@@ -7290,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.095</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -7305,48 +7305,48 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.095</v>
+        <v>0.13</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.524</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.182</v>
+        <v>0.231</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>3.253</v>
+        <v>3.231</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.511</v>
+        <v>0.55</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.532</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.893</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="AS45" t="n">
         <v>0.161</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.455</v>
+        <v>0.417</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="AY45" t="n">
         <v>0.007</v>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -7386,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2.031</v>
+        <v>2.059</v>
       </c>
       <c r="L46" t="n">
-        <v>1.656</v>
+        <v>1.618</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7401,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -7518,118 +7518,118 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
-        <v>94.09399999999999</v>
+        <v>94.64700000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>21.75</v>
+        <v>22.118</v>
       </c>
       <c r="E47" t="n">
-        <v>37.562</v>
+        <v>37.882</v>
       </c>
       <c r="F47" t="n">
-        <v>11.719</v>
+        <v>11.706</v>
       </c>
       <c r="G47" t="n">
-        <v>32.594</v>
+        <v>32.412</v>
       </c>
       <c r="H47" t="n">
-        <v>15.438</v>
+        <v>15.294</v>
       </c>
       <c r="I47" t="n">
-        <v>21.625</v>
+        <v>21.412</v>
       </c>
       <c r="J47" t="n">
-        <v>20.75</v>
+        <v>20.618</v>
       </c>
       <c r="K47" t="n">
-        <v>26.219</v>
+        <v>26.324</v>
       </c>
       <c r="L47" t="n">
-        <v>14.125</v>
+        <v>13.853</v>
       </c>
       <c r="M47" t="n">
-        <v>7.844</v>
+        <v>7.941</v>
       </c>
       <c r="N47" t="n">
-        <v>6.5</v>
+        <v>6.471</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>12.281</v>
+        <v>12</v>
       </c>
       <c r="Q47" t="n">
-        <v>11.812</v>
+        <v>11.559</v>
       </c>
       <c r="R47" t="n">
-        <v>19.375</v>
+        <v>19.206</v>
       </c>
       <c r="S47" t="n">
-        <v>22.094</v>
+        <v>21.912</v>
       </c>
       <c r="T47" t="n">
-        <v>3747</v>
+        <v>4011</v>
       </c>
       <c r="U47" t="n">
-        <v>13.75</v>
+        <v>13.971</v>
       </c>
       <c r="V47" t="n">
-        <v>12.625</v>
+        <v>12.559</v>
       </c>
       <c r="W47" t="n">
-        <v>8.718999999999999</v>
+        <v>8.647</v>
       </c>
       <c r="X47" t="n">
-        <v>4.656</v>
+        <v>4.618</v>
       </c>
       <c r="Y47" t="n">
-        <v>30.438</v>
+        <v>30.529</v>
       </c>
       <c r="Z47" t="n">
-        <v>41.719</v>
+        <v>41.618</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.73</v>
+        <v>0.734</v>
       </c>
       <c r="AB47" t="n">
-        <v>4.625</v>
+        <v>4.676</v>
       </c>
       <c r="AC47" t="n">
-        <v>11.594</v>
+        <v>11.618</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.399</v>
+        <v>0.403</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.125</v>
+        <v>2.206</v>
       </c>
       <c r="AF47" t="n">
-        <v>5.875</v>
+        <v>6.059</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.062</v>
+        <v>3.059</v>
       </c>
       <c r="AI47" t="n">
-        <v>7.719</v>
+        <v>7.706</v>
       </c>
       <c r="AJ47" t="n">
         <v>0.397</v>
       </c>
       <c r="AK47" t="n">
-        <v>8.656000000000001</v>
+        <v>8.647</v>
       </c>
       <c r="AL47" t="n">
-        <v>24.875</v>
+        <v>24.706</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
@@ -7637,34 +7637,34 @@
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>91.952</v>
+        <v>91.715</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.591</v>
+        <v>0.594</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.023</v>
+        <v>1.032</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.22</v>
+        <v>0.218</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.69</v>
+        <v>1.718</v>
       </c>
       <c r="AV47" t="n">
         <v>0.2</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="AY47" t="n">
         <v>0</v>
@@ -7677,118 +7677,118 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
-        <v>83.46899999999999</v>
+        <v>83.206</v>
       </c>
       <c r="D48" t="n">
-        <v>20</v>
+        <v>20.088</v>
       </c>
       <c r="E48" t="n">
-        <v>37.312</v>
+        <v>37.441</v>
       </c>
       <c r="F48" t="n">
-        <v>9.843999999999999</v>
+        <v>9.765000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>30.125</v>
+        <v>29.941</v>
       </c>
       <c r="H48" t="n">
-        <v>13.938</v>
+        <v>13.735</v>
       </c>
       <c r="I48" t="n">
-        <v>18.25</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>16.75</v>
+        <v>16.294</v>
       </c>
       <c r="K48" t="n">
-        <v>23.75</v>
+        <v>23.735</v>
       </c>
       <c r="L48" t="n">
-        <v>11.188</v>
+        <v>11.147</v>
       </c>
       <c r="M48" t="n">
-        <v>6.438</v>
+        <v>6.353</v>
       </c>
       <c r="N48" t="n">
-        <v>6.469</v>
+        <v>6.441</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>13.656</v>
+        <v>13.647</v>
       </c>
       <c r="Q48" t="n">
-        <v>12.719</v>
+        <v>12.735</v>
       </c>
       <c r="R48" t="n">
-        <v>22.094</v>
+        <v>21.912</v>
       </c>
       <c r="S48" t="n">
-        <v>19.281</v>
+        <v>19.118</v>
       </c>
       <c r="T48" t="n">
-        <v>2870</v>
+        <v>3024</v>
       </c>
       <c r="U48" t="n">
-        <v>9.625</v>
+        <v>9.5</v>
       </c>
       <c r="V48" t="n">
-        <v>9.561999999999999</v>
+        <v>9.647</v>
       </c>
       <c r="W48" t="n">
-        <v>6.219</v>
+        <v>6.147</v>
       </c>
       <c r="X48" t="n">
-        <v>3.375</v>
+        <v>3.294</v>
       </c>
       <c r="Y48" t="n">
-        <v>26.781</v>
+        <v>26.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>36.781</v>
+        <v>36.265</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.031</v>
+        <v>5.176</v>
       </c>
       <c r="AC48" t="n">
-        <v>12.125</v>
+        <v>12.382</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.415</v>
+        <v>0.418</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.125</v>
+        <v>2.147</v>
       </c>
       <c r="AF48" t="n">
-        <v>6.656</v>
+        <v>6.794</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.319</v>
+        <v>0.316</v>
       </c>
       <c r="AH48" t="n">
-        <v>3.062</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="n">
-        <v>8.281000000000001</v>
+        <v>8.234999999999999</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.37</v>
+        <v>0.364</v>
       </c>
       <c r="AK48" t="n">
-        <v>6.781</v>
+        <v>6.765</v>
       </c>
       <c r="AL48" t="n">
-        <v>21.844</v>
+        <v>21.706</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.31</v>
+        <v>0.312</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
@@ -7796,25 +7796,25 @@
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>89.124</v>
+        <v>88.949</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.516</v>
+        <v>0.515</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.553</v>
+        <v>0.552</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AS48" t="n">
         <v>0.153</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.227</v>
+        <v>1.194</v>
       </c>
       <c r="AV48" t="n">
         <v>0.194</v>
